--- a/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
@@ -656,416 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>20400</v>
+      </c>
+      <c r="F8" s="3">
         <v>17400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>18600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>19400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>26800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>35200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>39500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>39700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>37700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>34600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>33700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>31400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>27000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>25500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>22100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>20700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>18400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>19800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>24800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>20200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>22200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>28600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>27100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>24400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>26300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>28200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>23600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>20600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>20300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F9" s="3">
         <v>15500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>16900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>14300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>18200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>20400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>24100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>26300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>25600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>23100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>21500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>19800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>17900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>16600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>15400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>15200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>14500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>14100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>16300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>13500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>16400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>18000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>16100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>14800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>16500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>17000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>16300</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>14300</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>12700</v>
       </c>
       <c r="AF9" s="3">
         <v>14300</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3">
+        <v>12700</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F10" s="3">
         <v>1900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>5100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>8600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>14800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>15400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>13400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>12100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>11500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>12200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>11600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>9100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>8900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>6700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>5500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>5700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>8500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>6700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>5800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>10600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>11000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>9600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>9800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>11200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>7300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>6300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>7600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1123,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F12" s="3">
         <v>2900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G12" s="3">
-        <v>3700</v>
       </c>
       <c r="H12" s="3">
         <v>3600</v>
       </c>
       <c r="I12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K12" s="3">
         <v>3500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>2600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>2500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>2000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1500</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>1300</v>
       </c>
       <c r="AB12" s="3">
         <v>1400</v>
       </c>
       <c r="AC12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AE12" s="3">
         <v>1000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1359,8 +1398,8 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1371,11 +1410,17 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>24000</v>
+      </c>
+      <c r="F17" s="3">
         <v>24100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>25400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>23800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>27800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>30600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>34200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>36000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>34700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>32200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>29800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>27800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>25100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>23300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>21700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>21400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>21200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>20300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>22500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>19600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>22900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>24300</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>22600</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>20500</v>
       </c>
       <c r="AA17" s="3">
         <v>22600</v>
       </c>
       <c r="AB17" s="3">
+        <v>20500</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>22600</v>
+      </c>
+      <c r="AD17" s="3">
         <v>22900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>21300</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>19200</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>18000</v>
       </c>
       <c r="AF17" s="3">
         <v>19200</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>19200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-6700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-6800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>4600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>5300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>3900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-2800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>2300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>4300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>4500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>3900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>3700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>5300</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>2300</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>1400</v>
       </c>
       <c r="AE18" s="3">
         <v>2300</v>
       </c>
       <c r="AF18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AH18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,192 +1780,206 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>3600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>9300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>9600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>6600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>5200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>6200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>7200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>6100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>3700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>5800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>6100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>4600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>4500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>5900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>3200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>3300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,192 +2070,210 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-6500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>7200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>7600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>4600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>4400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>4500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-2000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>4600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>4900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>3500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>3400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>4700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>2100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>300</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>300</v>
       </c>
       <c r="AD24" s="3">
         <v>200</v>
       </c>
       <c r="AE24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AF24" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-6400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>6700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>6500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>3600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>4100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>4600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>3200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>3300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>4600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>1800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>2000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>5500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>3100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>4300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>3400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>3900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>2800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>3100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>4400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>1900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>2200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2952,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>5500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>3100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>4300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>3400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>3900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>2800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>3100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>4400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>1900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>2200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>5500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>3100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>4300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>3400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>3900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>2800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>3100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>4400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>1900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>2200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,560 +3523,598 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>37800</v>
+      </c>
+      <c r="F41" s="3">
         <v>28500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>30100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>35400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>34900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>32900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>41000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>29500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>36800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>43600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>52800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>61200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>72600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>22400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>26500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>20100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>26900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>27800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>28700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>21100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>16500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>18000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>29700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>39200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>44400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>48100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>56500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>56500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>36200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F42" s="3">
         <v>4300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>7100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>7000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>9300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>7200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>4500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>5400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>5400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>5700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>4500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>5200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>8700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>9400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>6100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>7500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>13100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>22100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>21900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>18800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>15200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>20000</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>20500</v>
-      </c>
-      <c r="AC42" s="3">
-        <v>22500</v>
       </c>
       <c r="AD42" s="3">
         <v>20500</v>
       </c>
       <c r="AE42" s="3">
+        <v>22500</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>20500</v>
+      </c>
+      <c r="AG42" s="3">
         <v>11400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>19300</v>
+      </c>
+      <c r="F43" s="3">
         <v>18900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>19900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>21300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>29300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>38100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>38800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>39800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>34800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>36600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>33500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>28400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>24600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>22700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>19800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>23600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>19000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>17500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>18300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>19600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>19600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>23300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>22500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>21300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>22800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>20900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>18400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>17800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>14500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>85900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>86500</v>
+      </c>
+      <c r="F44" s="3">
         <v>86400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>87100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>91700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>89600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>88500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>77300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>68800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>65900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>60700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>58900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>54700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>51500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>48400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>49600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>48300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>49200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>49100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>50300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>53000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>58600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>58700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>57000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>51100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>45800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>40800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>40600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>39200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>40200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F45" s="3">
         <v>22300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>21400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>21500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>20400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>14700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>15800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>16500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>17300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>13100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>16500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>18400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>15600</v>
-      </c>
-      <c r="P45" s="3">
-        <v>10600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>9600</v>
       </c>
       <c r="R45" s="3">
         <v>10600</v>
       </c>
       <c r="S45" s="3">
+        <v>9600</v>
+      </c>
+      <c r="T45" s="3">
+        <v>10600</v>
+      </c>
+      <c r="U45" s="3">
         <v>8700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>8200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>6900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>11400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>11700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>10600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>9400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>6700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>7500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>5700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>5300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>4700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>5100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>163700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>170700</v>
+      </c>
+      <c r="F46" s="3">
         <v>160300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>165500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>177000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>183500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>181500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>177400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>160100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>160200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>159600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>164400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>163000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>164500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>108500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>110700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>111300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>113200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>108700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>111700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>118100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>128500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>132600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>137500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>133600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>140500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>136000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>143200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>138700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>107300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>101600</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3913,183 +4122,195 @@
         <v>13200</v>
       </c>
       <c r="E47" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F47" s="3">
+        <v>13200</v>
+      </c>
+      <c r="G47" s="3">
         <v>13400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>18100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>16700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>17900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>20900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>20700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>19700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>16000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>11200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>13000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>12100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>8700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>4700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>4000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>4000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>10600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>7700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>2600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>5200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>6300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>10000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>16800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>16900</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>13900</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>12800</v>
       </c>
       <c r="AD47" s="3">
         <v>13900</v>
       </c>
       <c r="AE47" s="3">
+        <v>12800</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>13900</v>
+      </c>
+      <c r="AG47" s="3">
         <v>11000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>20400</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>165800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>169100</v>
+      </c>
+      <c r="F48" s="3">
         <v>161700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>160100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>164200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>162800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>154500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>154900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>149500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>144700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>134000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>129700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>122500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>118500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>111000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>103800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>100300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>100300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>92700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>88600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>86000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>82300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>74800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>65200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>58800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>46500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>42300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>27900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>27100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>27800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4597,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F52" s="3">
         <v>7000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>7100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>7300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>7000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>7900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>8100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>8100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>7800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>6000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>7000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>7100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>5800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>5700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>5900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>7800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>7500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>6800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>7000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>7200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>7300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>7500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>7800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>7800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>8100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>349000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>358700</v>
+      </c>
+      <c r="F54" s="3">
         <v>342200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>346200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>366600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>370100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>361800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>361300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>338400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>332400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>315700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>309400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>301900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>298900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>232700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>226200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>222600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>223300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>217700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>213900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>214600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>223500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>220400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>219700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>216300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>211200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>199600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>191800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>187400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>154200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>152900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,171 +4967,179 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="F57" s="3">
         <v>10100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>14200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>17000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>24200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>14700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>19600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>12400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>17100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>18800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>16300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>13200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>12400</v>
-      </c>
-      <c r="R57" s="3">
-        <v>11000</v>
       </c>
       <c r="S57" s="3">
         <v>12400</v>
       </c>
       <c r="T57" s="3">
+        <v>11000</v>
+      </c>
+      <c r="U57" s="3">
+        <v>12400</v>
+      </c>
+      <c r="V57" s="3">
         <v>9500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>6200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>9600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>17400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>13500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>15300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>12000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>11400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>9500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>8200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>8200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>6700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>52900</v>
+      </c>
+      <c r="F58" s="3">
         <v>45800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>45600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>52800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>47100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>43000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>33000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>20200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>14100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>13300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>10500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>10400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>10400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>6100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>6100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>5700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>5600</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X58" s="3">
-        <v>300</v>
+      <c r="X58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>10</v>
+      <c r="Z58" s="3">
+        <v>300</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>10</v>
@@ -4883,206 +5150,224 @@
       <c r="AC58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F59" s="3">
         <v>11700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>11700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>12400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>14000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>13700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>11900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>14100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>11600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>10600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>10300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>9900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>9700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>8900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>9400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>8000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>10800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>7800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>11300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>11600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>10600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>9200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>11100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>9300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>9400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>7900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>9300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>81600</v>
+      </c>
+      <c r="F60" s="3">
         <v>67700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>67300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>72800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>75300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>72900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>70900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>46800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>47800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>37300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>38200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>39500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>39100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>26500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>28100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>26000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>27500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>23200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>16900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>17400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>28700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>25400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>25900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>21200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>22600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>18800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>17600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>16100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>16000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -5106,14 +5391,14 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -5168,73 +5453,79 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F62" s="3">
         <v>6400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>5000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>4300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>4400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1100</v>
-      </c>
-      <c r="W62" s="3">
-        <v>300</v>
-      </c>
-      <c r="X62" s="3">
-        <v>300</v>
       </c>
       <c r="Y62" s="3">
         <v>300</v>
@@ -5246,22 +5537,28 @@
         <v>300</v>
       </c>
       <c r="AB62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD62" s="3">
         <v>400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>147900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>154700</v>
+      </c>
+      <c r="F66" s="3">
         <v>138000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>136400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>146600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>148500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>144600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>144900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>122700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>120900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>109900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>109600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>106800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>106200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>37300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>37900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>35600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>35500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>30800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>22600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>23000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>32700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>29300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>30000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>26600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>27400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>23200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>21800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>20500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>21200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-28400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-22600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-17500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-14200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-15500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-21300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-26800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-30000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-32900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-36700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-41100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-44500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-47600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-48000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-47800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-45700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-44800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-46300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-45200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-44100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-48100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-52000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-54800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-58000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-62400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-64300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>197600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>200500</v>
+      </c>
+      <c r="F76" s="3">
         <v>200700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>206300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>216500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>218100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>213600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>212800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>212200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>208000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>202200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>196300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>191600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>189100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>191900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>184800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>183500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>184400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>183400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>187800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>188000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>187300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>187600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>186100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>186100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>180300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>172900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>166500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>163400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>129500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>5500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>3100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>4300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>3400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>3900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>2800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>3100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>4400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>1900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>2200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6814,10 +7211,10 @@
         <v>2200</v>
       </c>
       <c r="E83" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="F83" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="G83" s="3">
         <v>2100</v>
@@ -6826,58 +7223,58 @@
         <v>2100</v>
       </c>
       <c r="I83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="J83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="K83" s="3">
         <v>2000</v>
       </c>
       <c r="L83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N83" s="3">
         <v>1800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1400</v>
-      </c>
-      <c r="P83" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1000</v>
       </c>
       <c r="R83" s="3">
         <v>1000</v>
       </c>
       <c r="S83" s="3">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="T83" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="U83" s="3">
         <v>1400</v>
       </c>
       <c r="V83" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="W83" s="3">
         <v>1400</v>
       </c>
       <c r="X83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>1100</v>
       </c>
       <c r="AA83" s="3">
         <v>1100</v>
@@ -6892,13 +7289,19 @@
         <v>1100</v>
       </c>
       <c r="AE83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG83" s="3">
         <v>1200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-14800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>14400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-8900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>7400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-8300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>8100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-6100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>5300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>8800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>3400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>4800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>7000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7492,91 +7933,97 @@
         <v>-4400</v>
       </c>
       <c r="E91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-3600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-7900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-14600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-6300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-10600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-6100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-5800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-7700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-4300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-7800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-5700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-5300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-6300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-7200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-12100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-6300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-13300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-12800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-7300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-5500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-6300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-6600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-7600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>6900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-5200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8738,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-4100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>5800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>13200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>14100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>7900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>3900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>2600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>53600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>5800</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
-      </c>
-      <c r="X100" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-100</v>
       </c>
       <c r="Z100" s="3">
         <v>100</v>
       </c>
       <c r="AA100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC100" s="3">
         <v>2700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>32200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>800</v>
+      </c>
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1900</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>3400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>3500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>4500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-8100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>15400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-7300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-6800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-9200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-8400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-11400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>50200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>6500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-6800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>7700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>4500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-11700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-9500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>20400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>6500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>3500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E8" s="3">
         <v>22700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>18600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>26800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>39500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>39700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>37700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>31400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>27000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>25500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>19800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>24800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>28600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>24400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>26300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>28200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>23600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>20600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>20300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E9" s="3">
         <v>16600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>20400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>25600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>23100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>18000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>16300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E10" s="3">
         <v>6100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>10600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>11000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>11200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>7300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6300</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>7600</v>
       </c>
       <c r="AH10" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E12" s="3">
         <v>3200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
-      </c>
-      <c r="X12" s="3">
-        <v>1300</v>
       </c>
       <c r="Y12" s="3">
         <v>1300</v>
       </c>
       <c r="Z12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA12" s="3">
         <v>1700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1404,23 +1424,26 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E17" s="3">
         <v>26000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>29800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>20500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>22900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>19200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>18000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,204 +1815,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>800</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-300</v>
       </c>
       <c r="AH20" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="3">
         <v>400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>300</v>
       </c>
       <c r="F24" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="G24" s="3">
         <v>-100</v>
       </c>
       <c r="H24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>400</v>
       </c>
       <c r="AA24" s="3">
         <v>400</v>
       </c>
       <c r="AB24" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1400</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-1100</v>
       </c>
       <c r="Y27" s="3">
         <v>-1100</v>
       </c>
       <c r="Z27" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AA27" s="3">
         <v>3900</v>
       </c>
       <c r="AB27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AC27" s="3">
         <v>2800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>600</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>2200</v>
       </c>
       <c r="AH27" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-800</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>800</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>300</v>
       </c>
       <c r="AH32" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1400</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-1100</v>
       </c>
       <c r="Y33" s="3">
         <v>-1100</v>
       </c>
       <c r="Z33" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AA33" s="3">
         <v>3900</v>
       </c>
       <c r="AB33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AC33" s="3">
         <v>2800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>600</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>2200</v>
       </c>
       <c r="AH33" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1400</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-1100</v>
       </c>
       <c r="Y35" s="3">
         <v>-1100</v>
       </c>
       <c r="Z35" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AA35" s="3">
         <v>3900</v>
       </c>
       <c r="AB35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AC35" s="3">
         <v>2800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>600</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>2200</v>
       </c>
       <c r="AH35" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E41" s="3">
         <v>25800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>35400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>34900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>29500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>43600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>61200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>72600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>26500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>20100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>26900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>27800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>28700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>21100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>18000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>29700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>39200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>44400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>48100</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>56500</v>
       </c>
       <c r="AF41" s="3">
         <v>56500</v>
       </c>
       <c r="AG41" s="3">
+        <v>56500</v>
+      </c>
+      <c r="AH41" s="3">
         <v>36200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3632,685 +3722,706 @@
         <v>1700</v>
       </c>
       <c r="E42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F42" s="3">
         <v>2100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4500</v>
-      </c>
-      <c r="L42" s="3">
-        <v>5400</v>
       </c>
       <c r="M42" s="3">
         <v>5400</v>
       </c>
       <c r="N42" s="3">
+        <v>5400</v>
+      </c>
+      <c r="O42" s="3">
         <v>5700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2800</v>
-      </c>
-      <c r="P42" s="3">
-        <v>200</v>
       </c>
       <c r="Q42" s="3">
         <v>200</v>
       </c>
       <c r="R42" s="3">
+        <v>200</v>
+      </c>
+      <c r="S42" s="3">
         <v>4500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>5200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>8700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>9400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>6100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>7500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>13100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>22100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>21900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>18800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>15200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>20000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>20500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>22500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>20500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>11400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E43" s="3">
         <v>25100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>38100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>38800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>34800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>36600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>33500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>28400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>22700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>17500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>18300</v>
-      </c>
-      <c r="X43" s="3">
-        <v>19600</v>
       </c>
       <c r="Y43" s="3">
         <v>19600</v>
       </c>
       <c r="Z43" s="3">
+        <v>19600</v>
+      </c>
+      <c r="AA43" s="3">
         <v>23300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>22500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>21300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>22800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>20900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>18400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>17800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>14500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E44" s="3">
         <v>85900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>86500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>86400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>87100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>91700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>89600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>88500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>77300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>68800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>65900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>60700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>58900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>54700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>51500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>48400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>49600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>48300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>49200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>49100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>50300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>53000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>58600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>58700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>57000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>51100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>45800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>40800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>40600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>39200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>40200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E45" s="3">
         <v>25300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>18400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>11400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>11700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>9400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>167400</v>
+      </c>
+      <c r="E46" s="3">
         <v>163700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>170700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>160300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>165500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>177000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>183500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>181500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>177400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>160100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>160200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>159600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>164400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>163000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>164500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>108500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>110700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>111300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>113200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>108700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>111700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>118100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>128500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>132600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>137500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>133600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>140500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>136000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>143200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>138700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>107300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>101600</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E47" s="3">
         <v>13200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>18100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>17900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>19700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>16000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>12100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4700</v>
-      </c>
-      <c r="T47" s="3">
-        <v>4000</v>
       </c>
       <c r="U47" s="3">
         <v>4000</v>
       </c>
       <c r="V47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W47" s="3">
         <v>10600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>10000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>16800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>16900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>12800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>11000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>20400</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>163900</v>
+      </c>
+      <c r="E48" s="3">
         <v>165800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>169100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>161700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>160100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>164200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>162800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>154500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>154900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>149500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>144700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>134000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>129700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>122500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>118500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>111000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>103800</v>
-      </c>
-      <c r="T48" s="3">
-        <v>100300</v>
       </c>
       <c r="U48" s="3">
         <v>100300</v>
       </c>
       <c r="V48" s="3">
+        <v>100300</v>
+      </c>
+      <c r="W48" s="3">
         <v>92700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>88600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>86000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>82300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>74800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>65200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>58800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>46500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>42300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>27900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>27100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>27800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4612,97 +4732,100 @@
         <v>6200</v>
       </c>
       <c r="E52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F52" s="3">
         <v>6400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>8100</v>
       </c>
       <c r="L52" s="3">
         <v>8100</v>
       </c>
       <c r="M52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="N52" s="3">
         <v>7800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7500</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>7800</v>
       </c>
       <c r="AF52" s="3">
         <v>7800</v>
       </c>
       <c r="AG52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="AH52" s="3">
         <v>8100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>349400</v>
+      </c>
+      <c r="E54" s="3">
         <v>349000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>358700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>342200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>346200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>366600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>370100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>361800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>361300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>338400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>332400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>315700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>309400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>301900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>298900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>232700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>226200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>222600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>223300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>217700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>213900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>214600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>223500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>220400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>219700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>216300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>211200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>199600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>191800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>187400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>154200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>152900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,168 +5099,172 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E57" s="3">
         <v>11900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>17400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9500</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>8200</v>
       </c>
       <c r="AF57" s="3">
         <v>8200</v>
       </c>
       <c r="AG57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AH57" s="3">
         <v>6700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E58" s="3">
         <v>49000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>52900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>45800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>45600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>52800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>47100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>43000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>33000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10500</v>
-      </c>
-      <c r="P58" s="3">
-        <v>10400</v>
       </c>
       <c r="Q58" s="3">
         <v>10400</v>
       </c>
       <c r="R58" s="3">
+        <v>10400</v>
+      </c>
+      <c r="S58" s="3">
         <v>3400</v>
-      </c>
-      <c r="S58" s="3">
-        <v>6100</v>
       </c>
       <c r="T58" s="3">
         <v>6100</v>
       </c>
       <c r="U58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="V58" s="3">
         <v>5700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5600</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>10</v>
@@ -5138,11 +5272,11 @@
       <c r="Y58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA58" s="3">
         <v>300</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>10</v>
@@ -5156,8 +5290,8 @@
       <c r="AE58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
@@ -5165,213 +5299,222 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E59" s="3">
         <v>11100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>11700</v>
       </c>
       <c r="G59" s="3">
         <v>11700</v>
       </c>
       <c r="H59" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I59" s="3">
         <v>12400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E60" s="3">
         <v>72000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>81600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>67700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>67300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>72800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>75300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>72900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>70900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>47800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>37300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>39500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>39100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>28100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>27500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>16900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>17400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>28700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>25400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>25900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>21200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>22600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>18800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>17600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>16100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E61" s="3">
         <v>7000</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -5397,11 +5540,11 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5459,76 +5602,79 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3700</v>
-      </c>
-      <c r="O62" s="3">
-        <v>3800</v>
       </c>
       <c r="P62" s="3">
         <v>3800</v>
       </c>
       <c r="Q62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="R62" s="3">
         <v>4300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4500</v>
-      </c>
-      <c r="U62" s="3">
-        <v>3100</v>
       </c>
       <c r="V62" s="3">
         <v>3100</v>
       </c>
       <c r="W62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="X62" s="3">
         <v>1300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>300</v>
       </c>
       <c r="Z62" s="3">
         <v>300</v>
@@ -5543,22 +5689,25 @@
         <v>300</v>
       </c>
       <c r="AD62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE62" s="3">
         <v>400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>149700</v>
+      </c>
+      <c r="E66" s="3">
         <v>147900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>154700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>138000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>136400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>146600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>148500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>144600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>144900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>122700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>120900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>109900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>109600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>106800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>106200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>35600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>35500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>30800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>32700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>29300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>30000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>27400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>21800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>21200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-34100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-32000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-22600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-17500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-15500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-21300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-26800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-30000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-32900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-36700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-41100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-44500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-46600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-47600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-48000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-47800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-45700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-44800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-46300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-45200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-44100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-48100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-52000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-54800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-58000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-62400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-64300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>196100</v>
+      </c>
+      <c r="E76" s="3">
         <v>197600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>200500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>200700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>206300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>216500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>218100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>213600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>212800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>212200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>208000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>202200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>196300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>191600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>189100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>191900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>184800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>183500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>184400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>183400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>187800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>188000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>187300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>187600</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>186100</v>
       </c>
       <c r="AB76" s="3">
         <v>186100</v>
       </c>
       <c r="AC76" s="3">
+        <v>186100</v>
+      </c>
+      <c r="AD76" s="3">
         <v>180300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>172900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>166500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>163400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>129500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1400</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-1100</v>
       </c>
       <c r="Y81" s="3">
         <v>-1100</v>
       </c>
       <c r="Z81" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AA81" s="3">
         <v>3900</v>
       </c>
       <c r="AB81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AC81" s="3">
         <v>2800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>600</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>2200</v>
       </c>
       <c r="AH81" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7211,13 +7410,13 @@
         <v>2200</v>
       </c>
       <c r="E83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F83" s="3">
         <v>2300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2100</v>
       </c>
       <c r="H83" s="3">
         <v>2100</v>
@@ -7229,7 +7428,7 @@
         <v>2100</v>
       </c>
       <c r="K83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="L83" s="3">
         <v>2000</v>
@@ -7238,19 +7437,19 @@
         <v>2000</v>
       </c>
       <c r="N83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O83" s="3">
         <v>1800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1400</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1000</v>
       </c>
       <c r="S83" s="3">
         <v>1000</v>
@@ -7259,25 +7458,25 @@
         <v>1000</v>
       </c>
       <c r="U83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V83" s="3">
         <v>1400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>1100</v>
       </c>
       <c r="AB83" s="3">
         <v>1100</v>
@@ -7295,13 +7494,16 @@
         <v>1100</v>
       </c>
       <c r="AG83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AH83" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-500</v>
       </c>
       <c r="AH91" s="3">
         <v>-500</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>6900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>13200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>14100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>53600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1800</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5800</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>400</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>100</v>
       </c>
       <c r="Z100" s="3">
         <v>100</v>
       </c>
       <c r="AA100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>32200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1900</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF101" s="3">
         <v>100</v>
       </c>
       <c r="AG101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>50200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6800</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-900</v>
       </c>
       <c r="V102" s="3">
         <v>-900</v>
       </c>
       <c r="W102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X102" s="3">
         <v>7700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-9500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>20400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>AXTI</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E8" s="3">
         <v>27900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>39500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>39700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>37700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>27000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>25500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>19800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>24800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>28600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>27100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>24400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>26300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>28200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>23600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>20600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>20300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E9" s="3">
         <v>20300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>24100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>21500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>18000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>16500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>17000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>16300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>14300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7600</v>
+        <v>5700</v>
       </c>
       <c r="E10" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F10" s="3">
         <v>6100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>10600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>11000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>11200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>7300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6300</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>7600</v>
       </c>
       <c r="AI10" s="3">
         <v>7600</v>
       </c>
+      <c r="AJ10" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E12" s="3">
         <v>3800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>1300</v>
       </c>
       <c r="Z12" s="3">
         <v>1300</v>
       </c>
       <c r="AA12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB12" s="3">
         <v>1700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,31 +1358,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1427,46 +1447,49 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E17" s="3">
         <v>29800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>34700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>29800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>19600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>22600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>20500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>22600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>22900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>21300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>19200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>18000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,233 +1849,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N20" s="3">
+        <v>900</v>
+      </c>
+      <c r="O20" s="3">
+        <v>200</v>
+      </c>
+      <c r="P20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R20" s="3">
+        <v>900</v>
+      </c>
+      <c r="S20" s="3">
+        <v>600</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>900</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>2600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>900</v>
-      </c>
-      <c r="N20" s="3">
-        <v>200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>600</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>800</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>-300</v>
       </c>
       <c r="AI20" s="3">
         <v>-300</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="E21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>800</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="M21" s="3">
+        <v>9600</v>
+      </c>
+      <c r="N21" s="3">
+        <v>6600</v>
+      </c>
+      <c r="O21" s="3">
+        <v>5200</v>
+      </c>
+      <c r="P21" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>7200</v>
+      </c>
+      <c r="R21" s="3">
+        <v>6100</v>
+      </c>
+      <c r="S21" s="3">
+        <v>3900</v>
+      </c>
+      <c r="T21" s="3">
+        <v>3100</v>
+      </c>
+      <c r="U21" s="3">
+        <v>2900</v>
+      </c>
+      <c r="V21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X21" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA21" s="3">
         <v>400</v>
       </c>
-      <c r="F21" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="AB21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>3600</v>
       </c>
-      <c r="K21" s="3">
-        <v>9300</v>
-      </c>
-      <c r="L21" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M21" s="3">
-        <v>6600</v>
-      </c>
-      <c r="N21" s="3">
-        <v>5200</v>
-      </c>
-      <c r="O21" s="3">
-        <v>6200</v>
-      </c>
-      <c r="P21" s="3">
-        <v>7200</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>6100</v>
-      </c>
-      <c r="R21" s="3">
-        <v>3900</v>
-      </c>
-      <c r="S21" s="3">
-        <v>3100</v>
-      </c>
-      <c r="T21" s="3">
-        <v>2900</v>
-      </c>
-      <c r="U21" s="3">
-        <v>1600</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-700</v>
-      </c>
-      <c r="W21" s="3">
-        <v>900</v>
-      </c>
-      <c r="X21" s="3">
-        <v>3700</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>600</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>5800</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>6100</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>4600</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>4500</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>5900</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>3200</v>
-      </c>
-      <c r="AG21" s="3">
-        <v>1700</v>
-      </c>
-      <c r="AH21" s="3">
-        <v>3300</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>3600</v>
-      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>300</v>
       </c>
       <c r="F24" s="3">
         <v>300</v>
       </c>
       <c r="G24" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="H24" s="3">
         <v>-100</v>
       </c>
       <c r="I24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>400</v>
       </c>
       <c r="AB24" s="3">
         <v>400</v>
       </c>
       <c r="AC24" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z27" s="3">
         <v>-1100</v>
       </c>
       <c r="AA27" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AB27" s="3">
         <v>3900</v>
       </c>
       <c r="AC27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AD27" s="3">
         <v>2800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>600</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>2200</v>
       </c>
       <c r="AI27" s="3">
         <v>2200</v>
       </c>
+      <c r="AJ27" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G32" s="3">
+        <v>500</v>
+      </c>
+      <c r="H32" s="3">
+        <v>600</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>800</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>300</v>
       </c>
       <c r="AI32" s="3">
         <v>300</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1600</v>
+        <v>-2900</v>
       </c>
       <c r="E33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="F33" s="3">
-        <v>-3700</v>
-      </c>
       <c r="G33" s="3">
-        <v>-5900</v>
+        <v>-3600</v>
       </c>
       <c r="H33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="I33" s="3">
         <v>-5100</v>
       </c>
-      <c r="I33" s="3">
-        <v>-3400</v>
-      </c>
       <c r="J33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K33" s="3">
         <v>1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z33" s="3">
         <v>-1100</v>
       </c>
       <c r="AA33" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AB33" s="3">
         <v>3900</v>
       </c>
       <c r="AC33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AD33" s="3">
         <v>2800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>600</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>2200</v>
       </c>
       <c r="AI33" s="3">
         <v>2200</v>
       </c>
+      <c r="AJ33" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1600</v>
+        <v>-2900</v>
       </c>
       <c r="E35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="F35" s="3">
-        <v>-3700</v>
-      </c>
       <c r="G35" s="3">
-        <v>-5900</v>
+        <v>-3600</v>
       </c>
       <c r="H35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="I35" s="3">
         <v>-5100</v>
       </c>
-      <c r="I35" s="3">
-        <v>-3400</v>
-      </c>
       <c r="J35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K35" s="3">
         <v>1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z35" s="3">
         <v>-1100</v>
       </c>
       <c r="AA35" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AB35" s="3">
         <v>3900</v>
       </c>
       <c r="AC35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AD35" s="3">
         <v>2800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>600</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>2200</v>
       </c>
       <c r="AI35" s="3">
         <v>2200</v>
       </c>
+      <c r="AJ35" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,816 +3698,841 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E41" s="3">
         <v>27800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>37800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>34900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>61200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>72600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>22400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>26500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>26900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>27800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>28700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>21100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>18000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>29700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>39200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>44400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>48100</v>
-      </c>
-      <c r="AF41" s="3">
-        <v>56500</v>
       </c>
       <c r="AG41" s="3">
         <v>56500</v>
       </c>
       <c r="AH41" s="3">
+        <v>56500</v>
+      </c>
+      <c r="AI41" s="3">
         <v>36200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>1700</v>
       </c>
       <c r="F42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G42" s="3">
         <v>2100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4500</v>
-      </c>
-      <c r="M42" s="3">
-        <v>5400</v>
       </c>
       <c r="N42" s="3">
         <v>5400</v>
       </c>
       <c r="O42" s="3">
+        <v>5400</v>
+      </c>
+      <c r="P42" s="3">
         <v>5700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2800</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>200</v>
       </c>
       <c r="R42" s="3">
         <v>200</v>
       </c>
       <c r="S42" s="3">
+        <v>200</v>
+      </c>
+      <c r="T42" s="3">
         <v>4500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>5200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>8700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>9400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>6100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>7500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>13100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>22100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>21900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>18800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>15200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>20000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>20500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>22500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>20500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>11400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E43" s="3">
         <v>27200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>18900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>19900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>38100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>38800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>39800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>34800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>36600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>33500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>28400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>22700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>23600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>18300</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>19600</v>
       </c>
       <c r="Z43" s="3">
         <v>19600</v>
       </c>
       <c r="AA43" s="3">
+        <v>19600</v>
+      </c>
+      <c r="AB43" s="3">
         <v>23300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>22500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>21300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>22800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>20900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>18400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>17800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>14500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E44" s="3">
         <v>85800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>85900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>86500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>86400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>87100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>91700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>89600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>88500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>77300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>68800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>65900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>60700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>58900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>54700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>51500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>48400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>49600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>48300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>49200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>49100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>50300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>53000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>58600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>58700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>57000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>51100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>45800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>40800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>40600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>39200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>40200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>25000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>25300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>25000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>22300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>21400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>21500</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K45" s="3">
         <v>20400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>18400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>11400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>9400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>167900</v>
+      </c>
+      <c r="E46" s="3">
         <v>167400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>163700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>170700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>160300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>165500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>177000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>183500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>181500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>177400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>160100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>160200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>159600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>164400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>163000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>164500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>108500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>110700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>111300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>113200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>108700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>111700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>118100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>128500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>132600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>137500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>133600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>140500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>136000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>143200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>138700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>107300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>101600</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>11900</v>
+        <v>14100</v>
       </c>
       <c r="E47" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F47" s="3">
         <v>13200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13200</v>
       </c>
-      <c r="H47" s="3">
-        <v>13400</v>
-      </c>
       <c r="I47" s="3">
-        <v>18100</v>
+        <v>14000</v>
       </c>
       <c r="J47" s="3">
+        <v>18200</v>
+      </c>
+      <c r="K47" s="3">
         <v>16700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>17900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>19700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>16000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4700</v>
-      </c>
-      <c r="U47" s="3">
-        <v>4000</v>
       </c>
       <c r="V47" s="3">
         <v>4000</v>
       </c>
       <c r="W47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X47" s="3">
         <v>10600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>10000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>16800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>16900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>12800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>11000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>20400</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>168900</v>
+      </c>
+      <c r="E48" s="3">
         <v>163900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>165800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>169100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>161700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>160100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>164200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>162800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>154500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>154900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>149500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>144700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>134000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>129700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>122500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>118500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>111000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>103800</v>
-      </c>
-      <c r="U48" s="3">
-        <v>100300</v>
       </c>
       <c r="V48" s="3">
         <v>100300</v>
       </c>
       <c r="W48" s="3">
+        <v>100300</v>
+      </c>
+      <c r="X48" s="3">
         <v>92700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>88600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>86000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>82300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>74800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>65200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>58800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>46500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>42300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>27900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>27100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>27800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4435,7 +4546,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F52" s="3">
         <v>6200</v>
       </c>
-      <c r="E52" s="3">
-        <v>6200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>6400</v>
-      </c>
       <c r="G52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H52" s="3">
         <v>7000</v>
       </c>
-      <c r="H52" s="3">
-        <v>7100</v>
-      </c>
       <c r="I52" s="3">
+        <v>6600</v>
+      </c>
+      <c r="J52" s="3">
         <v>7300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>8100</v>
       </c>
       <c r="M52" s="3">
         <v>8100</v>
       </c>
       <c r="N52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="O52" s="3">
         <v>7800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7500</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>7800</v>
       </c>
       <c r="AG52" s="3">
         <v>7800</v>
       </c>
       <c r="AH52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="AI52" s="3">
         <v>8100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>355600</v>
+      </c>
+      <c r="E54" s="3">
         <v>349400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>349000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>358700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>342200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>346200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>366600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>370100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>361800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>361300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>338400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>332400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>315700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>309400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>301900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>298900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>232700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>226200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>222600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>223300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>217700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>213900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>214600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>223500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>220400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>219700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>216300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>211200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>199600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>191800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>187400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>154200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>152900</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,174 +5230,178 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>13100</v>
+        <v>12800</v>
       </c>
       <c r="E57" s="3">
-        <v>11900</v>
+        <v>11700</v>
       </c>
       <c r="F57" s="3">
-        <v>16900</v>
+        <v>10300</v>
       </c>
       <c r="G57" s="3">
-        <v>10100</v>
+        <v>9600</v>
       </c>
       <c r="H57" s="3">
-        <v>9900</v>
+        <v>6400</v>
       </c>
       <c r="I57" s="3">
-        <v>7500</v>
+        <v>4700</v>
       </c>
       <c r="J57" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K57" s="3">
         <v>14200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>17400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>15300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9500</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>8200</v>
       </c>
       <c r="AG57" s="3">
         <v>8200</v>
       </c>
       <c r="AH57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AI57" s="3">
         <v>6700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>50700</v>
+        <v>54500</v>
       </c>
       <c r="E58" s="3">
-        <v>49000</v>
+        <v>51200</v>
       </c>
       <c r="F58" s="3">
-        <v>52900</v>
+        <v>49500</v>
       </c>
       <c r="G58" s="3">
-        <v>45800</v>
+        <v>53400</v>
       </c>
       <c r="H58" s="3">
-        <v>45600</v>
+        <v>46200</v>
       </c>
       <c r="I58" s="3">
-        <v>52800</v>
+        <v>45900</v>
       </c>
       <c r="J58" s="3">
+        <v>53200</v>
+      </c>
+      <c r="K58" s="3">
         <v>47100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>43000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>33000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10500</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>10400</v>
       </c>
       <c r="R58" s="3">
         <v>10400</v>
       </c>
       <c r="S58" s="3">
+        <v>10400</v>
+      </c>
+      <c r="T58" s="3">
         <v>3400</v>
-      </c>
-      <c r="T58" s="3">
-        <v>6100</v>
       </c>
       <c r="U58" s="3">
         <v>6100</v>
       </c>
       <c r="V58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="W58" s="3">
         <v>5700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5600</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>10</v>
@@ -5275,11 +5409,11 @@
       <c r="Z58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB58" s="3">
         <v>300</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>10</v>
@@ -5293,8 +5427,8 @@
       <c r="AF58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -5302,233 +5436,242 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F59" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G59" s="3">
+        <v>11200</v>
+      </c>
+      <c r="H59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>14000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>13000</v>
+      </c>
+      <c r="M59" s="3">
+        <v>13700</v>
+      </c>
+      <c r="N59" s="3">
+        <v>11900</v>
+      </c>
+      <c r="O59" s="3">
+        <v>14100</v>
+      </c>
+      <c r="P59" s="3">
+        <v>11600</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>10600</v>
+      </c>
+      <c r="R59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="S59" s="3">
+        <v>12300</v>
+      </c>
+      <c r="T59" s="3">
+        <v>9900</v>
+      </c>
+      <c r="U59" s="3">
+        <v>9700</v>
+      </c>
+      <c r="V59" s="3">
+        <v>8900</v>
+      </c>
+      <c r="W59" s="3">
+        <v>9400</v>
+      </c>
+      <c r="X59" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Y59" s="3">
         <v>10800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="Z59" s="3">
+        <v>7800</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AB59" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>10600</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AE59" s="3">
         <v>11100</v>
       </c>
-      <c r="F59" s="3">
-        <v>11800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>11700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>11700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>12400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>14000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>13000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>13700</v>
-      </c>
-      <c r="M59" s="3">
-        <v>11900</v>
-      </c>
-      <c r="N59" s="3">
-        <v>14100</v>
-      </c>
-      <c r="O59" s="3">
-        <v>11600</v>
-      </c>
-      <c r="P59" s="3">
-        <v>10600</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>10300</v>
-      </c>
-      <c r="R59" s="3">
-        <v>12300</v>
-      </c>
-      <c r="S59" s="3">
-        <v>9900</v>
-      </c>
-      <c r="T59" s="3">
-        <v>9700</v>
-      </c>
-      <c r="U59" s="3">
-        <v>8900</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="AF59" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AG59" s="3">
         <v>9400</v>
       </c>
-      <c r="W59" s="3">
-        <v>8000</v>
-      </c>
-      <c r="X59" s="3">
-        <v>10800</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>7800</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>11300</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>11600</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>10600</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>9200</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>11100</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AH59" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AI59" s="3">
         <v>9300</v>
       </c>
-      <c r="AF59" s="3">
-        <v>9400</v>
-      </c>
-      <c r="AG59" s="3">
-        <v>7900</v>
-      </c>
-      <c r="AH59" s="3">
-        <v>9300</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E60" s="3">
         <v>74600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>72000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>81600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>67700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>67300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>72800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>75300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>72900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>70900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>46800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>47800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>37300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>39500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>39100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>26500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>28100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>26000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>27500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>23200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>16900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>17400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>28700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>25400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>25900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>21200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>22600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>18800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>17600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6700</v>
+        <v>8400</v>
       </c>
       <c r="E61" s="3">
-        <v>7000</v>
+        <v>8800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5543,11 +5686,11 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5605,79 +5748,82 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>9700</v>
+      </c>
+      <c r="G62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J62" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K62" s="3">
         <v>5000</v>
       </c>
-      <c r="E62" s="3">
-        <v>4900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>8000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>5500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>5000</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3700</v>
-      </c>
-      <c r="P62" s="3">
-        <v>3800</v>
       </c>
       <c r="Q62" s="3">
         <v>3800</v>
       </c>
       <c r="R62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="S62" s="3">
         <v>4300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4500</v>
-      </c>
-      <c r="V62" s="3">
-        <v>3100</v>
       </c>
       <c r="W62" s="3">
         <v>3100</v>
       </c>
       <c r="X62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Y62" s="3">
         <v>1300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>300</v>
       </c>
       <c r="AA62" s="3">
         <v>300</v>
@@ -5692,22 +5838,25 @@
         <v>300</v>
       </c>
       <c r="AE62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF62" s="3">
         <v>400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>149700</v>
+        <v>89400</v>
       </c>
       <c r="E66" s="3">
-        <v>147900</v>
+        <v>86300</v>
       </c>
       <c r="F66" s="3">
-        <v>154700</v>
+        <v>83900</v>
       </c>
       <c r="G66" s="3">
-        <v>138000</v>
+        <v>89600</v>
       </c>
       <c r="H66" s="3">
-        <v>136400</v>
+        <v>74100</v>
       </c>
       <c r="I66" s="3">
-        <v>146600</v>
+        <v>71800</v>
       </c>
       <c r="J66" s="3">
+        <v>78300</v>
+      </c>
+      <c r="K66" s="3">
         <v>148500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>144600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>144900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>122700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>120900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>109900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>109600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>106800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>106200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>37900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>35600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>35500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>30800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>22600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>32700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>29300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>30000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>27400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>23200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>21800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>21200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>3500</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-35600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-34100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-32000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-28400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-22600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-17500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-14200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-15500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-21300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-26800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-30000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-32900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-36700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-41100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-44500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-46600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-47600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-48000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-47800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-45700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-44800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-46300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-45200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-44100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-48100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-52000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-54800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-58000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-62400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-64300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>197200</v>
+      </c>
+      <c r="E76" s="3">
         <v>196100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>197600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>200500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>200700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>206300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>216500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>218100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>213600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>212800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>212200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>208000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>202200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>196300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>191600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>189100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>191900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>184800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>183500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>184400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>183400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>187800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>188000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>187300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>187600</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>186100</v>
       </c>
       <c r="AC76" s="3">
         <v>186100</v>
       </c>
       <c r="AD76" s="3">
+        <v>186100</v>
+      </c>
+      <c r="AE76" s="3">
         <v>180300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>172900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>166500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>163400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>129500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1600</v>
+        <v>-2900</v>
       </c>
       <c r="E81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="F81" s="3">
-        <v>-3700</v>
-      </c>
       <c r="G81" s="3">
-        <v>-5900</v>
+        <v>-3600</v>
       </c>
       <c r="H81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="I81" s="3">
         <v>-5100</v>
       </c>
-      <c r="I81" s="3">
-        <v>-3400</v>
-      </c>
       <c r="J81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K81" s="3">
         <v>1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z81" s="3">
         <v>-1100</v>
       </c>
       <c r="AA81" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AB81" s="3">
         <v>3900</v>
       </c>
       <c r="AC81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AD81" s="3">
         <v>2800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>600</v>
-      </c>
-      <c r="AH81" s="3">
-        <v>2200</v>
       </c>
       <c r="AI81" s="3">
         <v>2200</v>
       </c>
+      <c r="AJ81" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7410,28 +7609,28 @@
         <v>2200</v>
       </c>
       <c r="E83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="F83" s="3">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="G83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="H83" s="3">
         <v>2100</v>
       </c>
       <c r="I83" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="J83" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="K83" s="3">
         <v>2100</v>
       </c>
       <c r="L83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="M83" s="3">
         <v>2000</v>
@@ -7440,19 +7639,19 @@
         <v>2000</v>
       </c>
       <c r="O83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P83" s="3">
         <v>1800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1400</v>
-      </c>
-      <c r="S83" s="3">
-        <v>1000</v>
       </c>
       <c r="T83" s="3">
         <v>1000</v>
@@ -7461,25 +7660,25 @@
         <v>1000</v>
       </c>
       <c r="V83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W83" s="3">
         <v>1400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1200</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>1100</v>
       </c>
       <c r="AC83" s="3">
         <v>1100</v>
@@ -7497,13 +7696,16 @@
         <v>1100</v>
       </c>
       <c r="AH83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AI83" s="3">
         <v>1200</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>1200</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E89" s="3">
         <v>800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>7000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4400</v>
       </c>
-      <c r="F91" s="3">
-        <v>-700</v>
-      </c>
       <c r="G91" s="3">
+        <v>700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-4400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-500</v>
       </c>
       <c r="AI91" s="3">
         <v>-500</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>-500</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>6900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800</v>
+      </c>
+      <c r="E100" s="3">
         <v>1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>13200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>14100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>53600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1800</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5800</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>400</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>100</v>
       </c>
       <c r="AA100" s="3">
         <v>100</v>
       </c>
       <c r="AB100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>32200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E101" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>900</v>
+      </c>
+      <c r="H101" s="3">
+        <v>600</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>900</v>
+      </c>
+      <c r="L101" s="3">
+        <v>600</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>300</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>500</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S101" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T101" s="3">
+        <v>400</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W101" s="3">
+        <v>300</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
-        <v>800</v>
-      </c>
-      <c r="G101" s="3">
-        <v>400</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>900</v>
-      </c>
-      <c r="K101" s="3">
-        <v>600</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="AB101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R101" s="3">
-        <v>3400</v>
-      </c>
-      <c r="S101" s="3">
-        <v>400</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V101" s="3">
-        <v>300</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AA101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>300</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>200</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG101" s="3">
         <v>100</v>
       </c>
       <c r="AH101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E102" s="3">
         <v>2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>50200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6800</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-900</v>
       </c>
       <c r="W102" s="3">
         <v>-900</v>
       </c>
       <c r="X102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Y102" s="3">
         <v>7700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>20400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>6500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>AXTI</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E8" s="3">
         <v>23600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>27900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>18600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>35200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>39500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>39700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>37700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>27000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>25500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>22100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>20700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>19800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>24800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>20200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>22200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>28600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>27100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>24400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>26300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>28200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>23600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>20600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>20300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E9" s="3">
         <v>18000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>25600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>23100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>18000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>14800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>16500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>17000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>16300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>12700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E10" s="3">
         <v>5700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>10600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>11000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>9800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>11200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6300</v>
-      </c>
-      <c r="AI10" s="3">
-        <v>7600</v>
       </c>
       <c r="AJ10" s="3">
         <v>7600</v>
       </c>
+      <c r="AK10" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E12" s="3">
         <v>3400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>1300</v>
       </c>
       <c r="AA12" s="3">
         <v>1300</v>
       </c>
       <c r="AB12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC12" s="3">
         <v>1700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1375,8 +1394,8 @@
       <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
@@ -1387,8 +1406,8 @@
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1450,49 +1469,52 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E15" s="3">
         <v>2300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2200</v>
       </c>
       <c r="F15" s="3">
         <v>2200</v>
       </c>
       <c r="G15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H15" s="3">
         <v>2300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2100</v>
       </c>
       <c r="J15" s="3">
         <v>2100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E17" s="3">
         <v>27100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>30600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>29800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>20300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>19600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>20500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>22600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>22900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>21300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>19200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,230 +1882,237 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O20" s="3">
+        <v>900</v>
+      </c>
+      <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S20" s="3">
+        <v>900</v>
+      </c>
+      <c r="T20" s="3">
+        <v>600</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X20" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>2600</v>
-      </c>
-      <c r="M20" s="3">
-        <v>2300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="R20" s="3">
-        <v>900</v>
-      </c>
-      <c r="S20" s="3">
-        <v>600</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>800</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>400</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>-300</v>
       </c>
       <c r="AJ20" s="3">
         <v>-300</v>
       </c>
+      <c r="AK20" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E21" s="3">
         <v>400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
         <v>400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>300</v>
       </c>
       <c r="F22" s="3">
         <v>300</v>
       </c>
       <c r="G22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H22" s="3">
         <v>400</v>
@@ -2085,7 +2124,7 @@
         <v>400</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2162,216 +2201,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>300</v>
       </c>
       <c r="G24" s="3">
         <v>300</v>
       </c>
       <c r="H24" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="I24" s="3">
         <v>-100</v>
       </c>
       <c r="J24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>400</v>
       </c>
       <c r="AC24" s="3">
         <v>400</v>
       </c>
       <c r="AD24" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE24" s="3">
         <v>300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-1100</v>
       </c>
       <c r="AA27" s="3">
         <v>-1100</v>
       </c>
       <c r="AB27" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AC27" s="3">
         <v>3900</v>
       </c>
       <c r="AD27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AE27" s="3">
         <v>2800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>600</v>
-      </c>
-      <c r="AI27" s="3">
-        <v>2200</v>
       </c>
       <c r="AJ27" s="3">
         <v>2200</v>
       </c>
+      <c r="AK27" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U32" s="3">
+        <v>100</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
-        <v>600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T32" s="3">
-        <v>100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>400</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>400</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>500</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>800</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>300</v>
       </c>
       <c r="AJ32" s="3">
         <v>300</v>
       </c>
+      <c r="AK32" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-1100</v>
       </c>
       <c r="AA33" s="3">
         <v>-1100</v>
       </c>
       <c r="AB33" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AC33" s="3">
         <v>3900</v>
       </c>
       <c r="AD33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AE33" s="3">
         <v>2800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>600</v>
-      </c>
-      <c r="AI33" s="3">
-        <v>2200</v>
       </c>
       <c r="AJ33" s="3">
         <v>2200</v>
       </c>
+      <c r="AK33" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-1100</v>
       </c>
       <c r="AA35" s="3">
         <v>-1100</v>
       </c>
       <c r="AB35" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AC35" s="3">
         <v>3900</v>
       </c>
       <c r="AD35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AE35" s="3">
         <v>2800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>600</v>
-      </c>
-      <c r="AI35" s="3">
-        <v>2200</v>
       </c>
       <c r="AJ35" s="3">
         <v>2200</v>
       </c>
+      <c r="AK35" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E41" s="3">
         <v>24900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>27800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>34900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>61200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>72600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>22400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>26500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>20100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>26900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>27800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>28700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>21100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>18000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>29700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>39200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>44400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>48100</v>
-      </c>
-      <c r="AG41" s="3">
-        <v>56500</v>
       </c>
       <c r="AH41" s="3">
         <v>56500</v>
       </c>
       <c r="AI41" s="3">
+        <v>56500</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3812,311 +3901,320 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>1700</v>
       </c>
       <c r="G42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H42" s="3">
         <v>2100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4500</v>
-      </c>
-      <c r="N42" s="3">
-        <v>5400</v>
       </c>
       <c r="O42" s="3">
         <v>5400</v>
       </c>
       <c r="P42" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Q42" s="3">
         <v>5700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2800</v>
-      </c>
-      <c r="R42" s="3">
-        <v>200</v>
       </c>
       <c r="S42" s="3">
         <v>200</v>
       </c>
       <c r="T42" s="3">
+        <v>200</v>
+      </c>
+      <c r="U42" s="3">
         <v>4500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>5200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>8700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>9400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>6100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>7500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>13100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>22100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>21900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>18800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>15200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>20000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>20500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>22500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>20500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E43" s="3">
         <v>28000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>18900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>21300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>38100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>38800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>39800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>34800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>36600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>33500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>28400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>22700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>23600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>18300</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>19600</v>
       </c>
       <c r="AA43" s="3">
         <v>19600</v>
       </c>
       <c r="AB43" s="3">
+        <v>19600</v>
+      </c>
+      <c r="AC43" s="3">
         <v>23300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>22500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>21300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>22800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>20900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>18400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>17800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>14500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>85100</v>
+      </c>
+      <c r="E44" s="3">
         <v>86100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>85800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>85900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>86500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>86400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>87100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>91700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>89600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>88500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>77300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>68800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>65900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>60700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>58900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>54700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>51500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>48400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>49600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>48300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>49200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>49100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>50300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>53000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>58600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>58700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>57000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>51100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>45800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>40800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>40600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>39200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>40200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,403 +4239,415 @@
       <c r="J45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="3">
         <v>20400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>18400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>10600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>9400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>158300</v>
+      </c>
+      <c r="E46" s="3">
         <v>167900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>167400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>163700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>170700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>160300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>165500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>177000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>183500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>181500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>177400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>160100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>160200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>159600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>164400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>163000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>164500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>108500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>110700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>111300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>113200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>108700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>111700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>118100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>128500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>132600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>137500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>133600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>140500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>136000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>143200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>138700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>107300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>101600</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E47" s="3">
         <v>14100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13200</v>
       </c>
-      <c r="G47" s="3">
-        <v>12500</v>
-      </c>
       <c r="H47" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I47" s="3">
         <v>13200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>18200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>17900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>19700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>16000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4700</v>
-      </c>
-      <c r="V47" s="3">
-        <v>4000</v>
       </c>
       <c r="W47" s="3">
         <v>4000</v>
       </c>
       <c r="X47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Y47" s="3">
         <v>10600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>10000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>16800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>16900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>12800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>13900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>20400</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>162200</v>
+      </c>
+      <c r="E48" s="3">
         <v>168900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>163900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>165800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>169100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>161700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>160100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>164200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>162800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>154500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>154900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>149500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>144700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>134000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>129700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>122500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>118500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>111000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>103800</v>
-      </c>
-      <c r="V48" s="3">
-        <v>100300</v>
       </c>
       <c r="W48" s="3">
         <v>100300</v>
       </c>
       <c r="X48" s="3">
+        <v>100300</v>
+      </c>
+      <c r="Y48" s="3">
         <v>92700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>88600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>86000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>82300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>74800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>65200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>58800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>46500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>42300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>27900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>27100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>27800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4546,11 +4656,11 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>1800</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E52" s="3">
         <v>4700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6200</v>
       </c>
-      <c r="G52" s="3">
-        <v>2900</v>
-      </c>
       <c r="H52" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I52" s="3">
         <v>7000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7900</v>
-      </c>
-      <c r="M52" s="3">
-        <v>8100</v>
       </c>
       <c r="N52" s="3">
         <v>8100</v>
       </c>
       <c r="O52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="P52" s="3">
         <v>7800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7500</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>7800</v>
       </c>
       <c r="AH52" s="3">
         <v>7800</v>
       </c>
       <c r="AI52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>339300</v>
+      </c>
+      <c r="E54" s="3">
         <v>355600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>349400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>349000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>358700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>342200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>346200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>366600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>370100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>361800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>361300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>338400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>332400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>315700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>309400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>301900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>298900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>232700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>226200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>222600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>223300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>217700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>213900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>214600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>223500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>220400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>219700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>216300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>211200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>199600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>191800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>187400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>154200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>152900</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,180 +5360,184 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E57" s="3">
         <v>12800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>16300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>17400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>15300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9500</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>8200</v>
       </c>
       <c r="AH57" s="3">
         <v>8200</v>
       </c>
       <c r="AI57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E58" s="3">
         <v>54500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>51200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>49500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>53400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>46200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>45900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>53200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>47100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>43000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>33000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>20200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10500</v>
-      </c>
-      <c r="R58" s="3">
-        <v>10400</v>
       </c>
       <c r="S58" s="3">
         <v>10400</v>
       </c>
       <c r="T58" s="3">
+        <v>10400</v>
+      </c>
+      <c r="U58" s="3">
         <v>3400</v>
-      </c>
-      <c r="U58" s="3">
-        <v>6100</v>
       </c>
       <c r="V58" s="3">
         <v>6100</v>
       </c>
       <c r="W58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="X58" s="3">
         <v>5700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5600</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>10</v>
@@ -5412,11 +5545,11 @@
       <c r="AA58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC58" s="3">
         <v>300</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>10</v>
@@ -5430,8 +5563,8 @@
       <c r="AG58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
+      <c r="AH58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AI58" s="3">
         <v>0</v>
@@ -5439,243 +5572,252 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E59" s="3">
         <v>5800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E60" s="3">
         <v>78800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>74600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>72000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>81600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>67700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>67300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>72800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>75300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>72900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>70900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>46800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>37300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>39500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>39100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>28100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>27500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>23200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>16900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>17400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>28700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>25400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>25900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>21200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>22600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>18800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>17600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E61" s="3">
         <v>8400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2200</v>
-      </c>
-      <c r="G61" s="3">
-        <v>4500</v>
       </c>
       <c r="H61" s="3">
         <v>2400</v>
       </c>
       <c r="I61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J61" s="3">
         <v>1200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5689,11 +5831,11 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5751,82 +5893,85 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E62" s="3">
         <v>2200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K62" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L62" s="3">
+        <v>5000</v>
+      </c>
+      <c r="M62" s="3">
         <v>3500</v>
       </c>
-      <c r="H62" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>4200</v>
-      </c>
-      <c r="K62" s="3">
-        <v>5000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>3500</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3700</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>3800</v>
       </c>
       <c r="R62" s="3">
         <v>3800</v>
       </c>
       <c r="S62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="T62" s="3">
         <v>4300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4500</v>
-      </c>
-      <c r="W62" s="3">
-        <v>3100</v>
       </c>
       <c r="X62" s="3">
         <v>3100</v>
       </c>
       <c r="Y62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Z62" s="3">
         <v>1300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>300</v>
       </c>
       <c r="AB62" s="3">
         <v>300</v>
@@ -5841,22 +5986,25 @@
         <v>300</v>
       </c>
       <c r="AF62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG62" s="3">
         <v>400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>84400</v>
+      </c>
+      <c r="E66" s="3">
         <v>89400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>86300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>83900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>89600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>71800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>78300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>148500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>144600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>144900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>122700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>120900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>109900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>109600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>106800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>106200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>37300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>37900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>35600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>35500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>30800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>32700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>29300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>30000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>26600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>27400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>21800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>20500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>21200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>3500</v>
       </c>
+      <c r="AK70" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-38600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-35600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-34100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-32000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-28400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-22600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-17500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-14200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-21300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-26800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-30000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-36700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-41100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-44500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-46600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-47600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-48000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-47800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-45700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-44800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-46300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-45200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-44100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-48100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-52000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-54800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-58000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-62400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-64300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>189200</v>
+      </c>
+      <c r="E76" s="3">
         <v>197200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>196100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>197600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>200500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>200700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>206300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>216500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>218100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>213600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>212800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>212200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>208000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>202200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>196300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>191600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>189100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>191900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>184800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>183500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>184400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>183400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>187800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>188000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>187300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>187600</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>186100</v>
       </c>
       <c r="AD76" s="3">
         <v>186100</v>
       </c>
       <c r="AE76" s="3">
+        <v>186100</v>
+      </c>
+      <c r="AF76" s="3">
         <v>180300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>172900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>166500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>163400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>129500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1400</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-1100</v>
       </c>
       <c r="AA81" s="3">
         <v>-1100</v>
       </c>
       <c r="AB81" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AC81" s="3">
         <v>3900</v>
       </c>
       <c r="AD81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AE81" s="3">
         <v>2800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>600</v>
-      </c>
-      <c r="AI81" s="3">
-        <v>2200</v>
       </c>
       <c r="AJ81" s="3">
         <v>2200</v>
       </c>
+      <c r="AK81" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,16 +7797,17 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E83" s="3">
         <v>2200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2100</v>
       </c>
       <c r="F83" s="3">
         <v>2100</v>
@@ -7621,19 +7819,19 @@
         <v>2100</v>
       </c>
       <c r="I83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="J83" s="3">
         <v>2000</v>
       </c>
       <c r="K83" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="L83" s="3">
         <v>2100</v>
       </c>
       <c r="M83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="N83" s="3">
         <v>2000</v>
@@ -7642,19 +7840,19 @@
         <v>2000</v>
       </c>
       <c r="P83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1400</v>
-      </c>
-      <c r="T83" s="3">
-        <v>1000</v>
       </c>
       <c r="U83" s="3">
         <v>1000</v>
@@ -7663,25 +7861,25 @@
         <v>1000</v>
       </c>
       <c r="W83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X83" s="3">
         <v>1400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>1100</v>
       </c>
       <c r="AD83" s="3">
         <v>1100</v>
@@ -7699,13 +7897,16 @@
         <v>1100</v>
       </c>
       <c r="AI83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AJ83" s="3">
         <v>1200</v>
       </c>
+      <c r="AK83" s="3">
+        <v>1200</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-14700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>-500</v>
       </c>
       <c r="AJ91" s="3">
         <v>-500</v>
       </c>
+      <c r="AK91" s="3">
+        <v>-500</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>6900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>13200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>14100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>53600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1800</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5800</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>400</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>100</v>
       </c>
       <c r="AB100" s="3">
         <v>100</v>
       </c>
       <c r="AC100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>32200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1900</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH101" s="3">
         <v>100</v>
       </c>
       <c r="AI101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>50200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6800</v>
-      </c>
-      <c r="W102" s="3">
-        <v>-900</v>
       </c>
       <c r="X102" s="3">
         <v>-900</v>
       </c>
       <c r="Y102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Z102" s="3">
         <v>7700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-9500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AG102" s="3">
-        <v>0</v>
-      </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>20400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>AXTI</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E8" s="3">
         <v>25100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>27900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>26800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>35200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>39500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>39700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>37700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>31400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>27000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>25500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>20700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>19800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>24800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>20200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>22200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>28600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>27100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>24400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>26300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>28200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>23600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>20600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>20300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E9" s="3">
         <v>20700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>25600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>23100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>18000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>16100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>14800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>16500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>17000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>16300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>12700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E10" s="3">
         <v>4400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>10600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>11000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>9600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>9800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>11200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>7300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6300</v>
-      </c>
-      <c r="AJ10" s="3">
-        <v>7600</v>
       </c>
       <c r="AK10" s="3">
         <v>7600</v>
       </c>
+      <c r="AL10" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,115 +1179,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E12" s="3">
         <v>4100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>1300</v>
       </c>
       <c r="AB12" s="3">
         <v>1300</v>
       </c>
       <c r="AC12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD12" s="3">
         <v>1700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1409,8 +1429,8 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1472,23 +1492,26 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1496,28 +1519,28 @@
         <v>2200</v>
       </c>
       <c r="E15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F15" s="3">
         <v>2300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2200</v>
       </c>
       <c r="G15" s="3">
         <v>2200</v>
       </c>
       <c r="H15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I15" s="3">
         <v>2300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2200</v>
-      </c>
-      <c r="J15" s="3">
-        <v>2100</v>
       </c>
       <c r="K15" s="3">
         <v>2100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E17" s="3">
         <v>31300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>34200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>34700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>20300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>19600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>22900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>22600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>20500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>22600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>22900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>21300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>19200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>18000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>5300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,222 +1916,229 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>-300</v>
       </c>
       <c r="AK20" s="3">
         <v>-300</v>
       </c>
+      <c r="AL20" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2106,16 +2146,16 @@
         <v>300</v>
       </c>
       <c r="E22" s="3">
+        <v>300</v>
+      </c>
+      <c r="F22" s="3">
         <v>400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>300</v>
       </c>
       <c r="G22" s="3">
         <v>300</v>
       </c>
       <c r="H22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I22" s="3">
         <v>400</v>
@@ -2127,7 +2167,7 @@
         <v>400</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2204,115 +2244,121 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2320,106 +2366,109 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>300</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
       </c>
       <c r="I24" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="J24" s="3">
         <v>-100</v>
       </c>
       <c r="K24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>400</v>
       </c>
       <c r="AD24" s="3">
         <v>400</v>
       </c>
       <c r="AE24" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
-      </c>
       <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-1100</v>
       </c>
       <c r="AB27" s="3">
         <v>-1100</v>
       </c>
       <c r="AC27" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AD27" s="3">
         <v>3900</v>
       </c>
       <c r="AE27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AF27" s="3">
         <v>2800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>600</v>
-      </c>
-      <c r="AJ27" s="3">
-        <v>2200</v>
       </c>
       <c r="AK27" s="3">
         <v>2200</v>
       </c>
+      <c r="AL27" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>800</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>300</v>
       </c>
       <c r="AK32" s="3">
         <v>300</v>
       </c>
+      <c r="AL32" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-1100</v>
       </c>
       <c r="AB33" s="3">
         <v>-1100</v>
       </c>
       <c r="AC33" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AD33" s="3">
         <v>3900</v>
       </c>
       <c r="AE33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AF33" s="3">
         <v>2800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>600</v>
-      </c>
-      <c r="AJ33" s="3">
-        <v>2200</v>
       </c>
       <c r="AK33" s="3">
         <v>2200</v>
       </c>
+      <c r="AL33" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-1100</v>
       </c>
       <c r="AB35" s="3">
         <v>-1100</v>
       </c>
       <c r="AC35" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AD35" s="3">
         <v>3900</v>
       </c>
       <c r="AE35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AF35" s="3">
         <v>2800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>600</v>
-      </c>
-      <c r="AJ35" s="3">
-        <v>2200</v>
       </c>
       <c r="AK35" s="3">
         <v>2200</v>
       </c>
+      <c r="AL35" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E41" s="3">
         <v>22800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>27800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>32900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>52800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>61200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>72600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>22400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>26500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>20100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>26900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>27800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>28700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>21100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>18000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>29700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>39200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>44400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>48100</v>
-      </c>
-      <c r="AH41" s="3">
-        <v>56500</v>
       </c>
       <c r="AI41" s="3">
         <v>56500</v>
       </c>
       <c r="AJ41" s="3">
+        <v>56500</v>
+      </c>
+      <c r="AK41" s="3">
         <v>36200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3904,317 +3994,326 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>1700</v>
       </c>
       <c r="H42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I42" s="3">
         <v>2100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4500</v>
-      </c>
-      <c r="O42" s="3">
-        <v>5400</v>
       </c>
       <c r="P42" s="3">
         <v>5400</v>
       </c>
       <c r="Q42" s="3">
+        <v>5400</v>
+      </c>
+      <c r="R42" s="3">
         <v>5700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2800</v>
-      </c>
-      <c r="S42" s="3">
-        <v>200</v>
       </c>
       <c r="T42" s="3">
         <v>200</v>
       </c>
       <c r="U42" s="3">
+        <v>200</v>
+      </c>
+      <c r="V42" s="3">
         <v>4500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>5200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>8700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>9400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>6100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>7500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>13100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>22100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>21900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>18800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>15200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>20000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>20500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>22500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>20500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>11400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E43" s="3">
         <v>25600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>19300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>19900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>38100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>38800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>39800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>34800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>36600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>33500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>28400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>24600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>22700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>23600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>19000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>17500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>18300</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>19600</v>
       </c>
       <c r="AB43" s="3">
         <v>19600</v>
       </c>
       <c r="AC43" s="3">
+        <v>19600</v>
+      </c>
+      <c r="AD43" s="3">
         <v>23300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>22500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>22800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>20900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>18400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>14500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E44" s="3">
         <v>85100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>86100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>85800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>85900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>86500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>86400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>87100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>91700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>89600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>88500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>77300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>68800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>65900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>60700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>58900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>54700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>51500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>48400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>49600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>48300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>49200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>49100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>50300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>53000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>58600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>58700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>57000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>51100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>45800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>40800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>40600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>39200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>40200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4242,416 +4341,428 @@
       <c r="K45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M45" s="3">
         <v>20400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>18400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>11700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>10600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>149500</v>
+      </c>
+      <c r="E46" s="3">
         <v>158300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>167900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>167400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>163700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>170700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>160300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>165500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>177000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>183500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>181500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>177400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>160100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>160200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>159600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>164400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>163000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>164500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>108500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>110700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>111300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>113200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>108700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>111700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>118100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>128500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>132600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>137500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>133600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>140500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>136000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>143200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>138700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>107300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>101600</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3">
         <v>14600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>18200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>16700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>17900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>19700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>16000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4700</v>
-      </c>
-      <c r="W47" s="3">
-        <v>4000</v>
       </c>
       <c r="X47" s="3">
         <v>4000</v>
       </c>
       <c r="Y47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Z47" s="3">
         <v>10600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>10000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>16800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>16900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>12800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>13900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>11000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>20400</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>161400</v>
+      </c>
+      <c r="E48" s="3">
         <v>162200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>168900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>163900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>165800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>169100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>161700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>160100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>164200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>162800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>154500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>154900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>149500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>144700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>134000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>129700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>122500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>118500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>111000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>103800</v>
-      </c>
-      <c r="W48" s="3">
-        <v>100300</v>
       </c>
       <c r="X48" s="3">
         <v>100300</v>
       </c>
       <c r="Y48" s="3">
+        <v>100300</v>
+      </c>
+      <c r="Z48" s="3">
         <v>92700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>88600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>86000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>82300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>74800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>65200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>58800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>46500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>42300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>27900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>27100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>27800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>1700</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
@@ -4659,11 +4770,11 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>1800</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7900</v>
-      </c>
-      <c r="N52" s="3">
-        <v>8100</v>
       </c>
       <c r="O52" s="3">
         <v>8100</v>
       </c>
       <c r="P52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>7800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7500</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>7800</v>
       </c>
       <c r="AI52" s="3">
         <v>7800</v>
       </c>
       <c r="AJ52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="AK52" s="3">
         <v>8100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>333500</v>
+      </c>
+      <c r="E54" s="3">
         <v>339300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>355600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>349400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>349000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>358700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>342200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>346200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>366600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>370100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>361800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>361300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>338400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>332400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>315700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>309400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>301900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>298900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>232700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>226200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>222600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>223300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>217700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>213900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>214600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>223500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>220400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>219700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>216300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>211200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>199600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>191800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>187400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>154200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>152900</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,186 +5491,190 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E57" s="3">
         <v>12400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>18800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>16300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>17400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>15300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9500</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>8200</v>
       </c>
       <c r="AI57" s="3">
         <v>8200</v>
       </c>
       <c r="AJ57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AK57" s="3">
         <v>6700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E58" s="3">
         <v>47800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>54500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>51200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>49500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>53400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>46200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>45900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>53200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>47100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>43000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>33000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>13300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>10500</v>
-      </c>
-      <c r="S58" s="3">
-        <v>10400</v>
       </c>
       <c r="T58" s="3">
         <v>10400</v>
       </c>
       <c r="U58" s="3">
+        <v>10400</v>
+      </c>
+      <c r="V58" s="3">
         <v>3400</v>
-      </c>
-      <c r="V58" s="3">
-        <v>6100</v>
       </c>
       <c r="W58" s="3">
         <v>6100</v>
       </c>
       <c r="X58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="Y58" s="3">
         <v>5700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5600</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>10</v>
@@ -5548,11 +5682,11 @@
       <c r="AB58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD58" s="3">
         <v>300</v>
-      </c>
-      <c r="AD58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>10</v>
@@ -5566,8 +5700,8 @@
       <c r="AH58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
@@ -5575,252 +5709,261 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="3">
         <v>7100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>9300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E60" s="3">
         <v>74200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>78800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>74600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>72000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>81600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>67700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>67300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>72800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>75300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>72900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>70900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>46800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>47800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>37300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>39500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>26500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>28100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>26000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>27500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>23200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>16900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>17400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>28700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>25400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>25900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>21200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>22600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>17600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>16100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>16000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E61" s="3">
         <v>7800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2200</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2400</v>
       </c>
       <c r="I61" s="3">
         <v>2400</v>
       </c>
       <c r="J61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K61" s="3">
         <v>1200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5834,11 +5977,11 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -5896,85 +6039,88 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E62" s="3">
         <v>2500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3700</v>
-      </c>
-      <c r="R62" s="3">
-        <v>3800</v>
       </c>
       <c r="S62" s="3">
         <v>3800</v>
       </c>
       <c r="T62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U62" s="3">
         <v>4300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4500</v>
-      </c>
-      <c r="X62" s="3">
-        <v>3100</v>
       </c>
       <c r="Y62" s="3">
         <v>3100</v>
       </c>
       <c r="Z62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AA62" s="3">
         <v>1300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>300</v>
       </c>
       <c r="AC62" s="3">
         <v>300</v>
@@ -5989,22 +6135,25 @@
         <v>300</v>
       </c>
       <c r="AG62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH62" s="3">
         <v>400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E66" s="3">
         <v>84400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>89400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>86300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>83900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>89600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>74100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>71800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>78300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>148500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>144600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>144900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>122700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>120900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>109900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>109600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>106800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>106200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>37300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>37900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>35600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>35500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>30800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>32700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>29300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>30000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>26600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>27400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>23200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>21800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>20500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>21200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>3500</v>
       </c>
+      <c r="AL70" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-43700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-38600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-35600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-34100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-32000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-28400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-22600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-17500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-14200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-15500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-21300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-26800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-32900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-36700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-41100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-44500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-46600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-47600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-48000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-47800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-45700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-44800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-46300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-45200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-44100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-48100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-52000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-54800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-58000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-62400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-64300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>181500</v>
+      </c>
+      <c r="E76" s="3">
         <v>189200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>197200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>196100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>197600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>200500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>200700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>206300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>216500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>218100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>213600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>212800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>212200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>208000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>202200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>196300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>191600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>189100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>191900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>184800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>183500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>184400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>183400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>187800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>188000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>187300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>187600</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>186100</v>
       </c>
       <c r="AE76" s="3">
         <v>186100</v>
       </c>
       <c r="AF76" s="3">
+        <v>186100</v>
+      </c>
+      <c r="AG76" s="3">
         <v>180300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>172900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>166500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>163400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>129500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1400</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-1100</v>
       </c>
       <c r="AB81" s="3">
         <v>-1100</v>
       </c>
       <c r="AC81" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AD81" s="3">
         <v>3900</v>
       </c>
       <c r="AE81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AF81" s="3">
         <v>2800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>600</v>
-      </c>
-      <c r="AJ81" s="3">
-        <v>2200</v>
       </c>
       <c r="AK81" s="3">
         <v>2200</v>
       </c>
+      <c r="AL81" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,19 +7996,20 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E83" s="3">
         <v>2300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2100</v>
       </c>
       <c r="G83" s="3">
         <v>2100</v>
@@ -7822,19 +8021,19 @@
         <v>2100</v>
       </c>
       <c r="J83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="K83" s="3">
         <v>2000</v>
       </c>
       <c r="L83" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="M83" s="3">
         <v>2100</v>
       </c>
       <c r="N83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="O83" s="3">
         <v>2000</v>
@@ -7843,19 +8042,19 @@
         <v>2000</v>
       </c>
       <c r="Q83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R83" s="3">
         <v>1800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1400</v>
-      </c>
-      <c r="U83" s="3">
-        <v>1000</v>
       </c>
       <c r="V83" s="3">
         <v>1000</v>
@@ -7864,25 +8063,25 @@
         <v>1000</v>
       </c>
       <c r="X83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>1100</v>
       </c>
       <c r="AE83" s="3">
         <v>1100</v>
@@ -7900,13 +8099,16 @@
         <v>1100</v>
       </c>
       <c r="AJ83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AK83" s="3">
         <v>1200</v>
       </c>
+      <c r="AL83" s="3">
+        <v>1200</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="3">
         <v>1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-10100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-14700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>-500</v>
       </c>
       <c r="AK91" s="3">
         <v>-500</v>
       </c>
+      <c r="AL91" s="3">
+        <v>-500</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>6900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>14100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>53600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1800</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>5800</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>400</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>100</v>
       </c>
       <c r="AC100" s="3">
         <v>100</v>
       </c>
       <c r="AD100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>32200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1900</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI101" s="3">
         <v>100</v>
       </c>
       <c r="AJ101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK101" s="3">
         <v>-900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>50200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>6500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6800</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-900</v>
       </c>
       <c r="Y102" s="3">
         <v>-900</v>
       </c>
       <c r="Z102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AA102" s="3">
         <v>7700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-9500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AH102" s="3">
-        <v>0</v>
-      </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>6500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>3500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>AXTI</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E8" s="3">
         <v>19400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>27900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>26800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>35200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>39500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>39700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>31400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>27000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>25500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>19800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>24800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>20200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>22200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>28600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>27100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>24400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>26300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>28200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>23600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>20600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>20300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E9" s="3">
         <v>20600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>25600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>23100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>17900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>18000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>16100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>16500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>17000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>14300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>12700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>10600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>11000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>9600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>9800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>11200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>6300</v>
-      </c>
-      <c r="AK10" s="3">
-        <v>7600</v>
       </c>
       <c r="AL10" s="3">
         <v>7600</v>
       </c>
+      <c r="AM10" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="3">
         <v>3100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1400</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>1300</v>
       </c>
       <c r="AC12" s="3">
         <v>1300</v>
       </c>
       <c r="AD12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE12" s="3">
         <v>1700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,8 +1452,8 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1495,55 +1515,58 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="E15" s="3">
         <v>2200</v>
       </c>
       <c r="F15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G15" s="3">
         <v>2300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2200</v>
       </c>
       <c r="H15" s="3">
         <v>2200</v>
       </c>
       <c r="I15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J15" s="3">
         <v>2300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2200</v>
-      </c>
-      <c r="K15" s="3">
-        <v>2100</v>
       </c>
       <c r="L15" s="3">
         <v>2100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E17" s="3">
         <v>29600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>31300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>26000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>30600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>36000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>34700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>27800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>23300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>20300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>19600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>22600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>20500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>22600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>22900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>21300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>19200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>18000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>5300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,248 +1950,255 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>800</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>-300</v>
       </c>
       <c r="AL20" s="3">
         <v>-300</v>
       </c>
+      <c r="AM20" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-7400</v>
+        <v>-4600</v>
       </c>
       <c r="E21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>5900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
         <v>300</v>
       </c>
       <c r="F22" s="3">
+        <v>300</v>
+      </c>
+      <c r="G22" s="3">
         <v>400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300</v>
       </c>
       <c r="H22" s="3">
         <v>300</v>
       </c>
       <c r="I22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J22" s="3">
         <v>400</v>
@@ -2170,7 +2210,7 @@
         <v>400</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2247,228 +2287,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>300</v>
       </c>
       <c r="I24" s="3">
         <v>300</v>
       </c>
       <c r="J24" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="K24" s="3">
         <v>-100</v>
       </c>
       <c r="L24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>400</v>
       </c>
       <c r="AE24" s="3">
         <v>400</v>
       </c>
       <c r="AF24" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG24" s="3">
         <v>300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>200</v>
       </c>
-      <c r="AK24" s="3">
-        <v>0</v>
-      </c>
       <c r="AL24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1400</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-1100</v>
       </c>
       <c r="AC27" s="3">
         <v>-1100</v>
       </c>
       <c r="AD27" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AE27" s="3">
         <v>3900</v>
       </c>
       <c r="AF27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AG27" s="3">
         <v>2800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>600</v>
-      </c>
-      <c r="AK27" s="3">
-        <v>2200</v>
       </c>
       <c r="AL27" s="3">
         <v>2200</v>
       </c>
+      <c r="AM27" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-800</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>1500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>800</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>300</v>
       </c>
       <c r="AL32" s="3">
         <v>300</v>
       </c>
+      <c r="AM32" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1400</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-1100</v>
       </c>
       <c r="AC33" s="3">
         <v>-1100</v>
       </c>
       <c r="AD33" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AE33" s="3">
         <v>3900</v>
       </c>
       <c r="AF33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AG33" s="3">
         <v>2800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>600</v>
-      </c>
-      <c r="AK33" s="3">
-        <v>2200</v>
       </c>
       <c r="AL33" s="3">
         <v>2200</v>
       </c>
+      <c r="AM33" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1400</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-1100</v>
       </c>
       <c r="AC35" s="3">
         <v>-1100</v>
       </c>
       <c r="AD35" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AE35" s="3">
         <v>3900</v>
       </c>
       <c r="AF35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AG35" s="3">
         <v>2800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>600</v>
-      </c>
-      <c r="AK35" s="3">
-        <v>2200</v>
       </c>
       <c r="AL35" s="3">
         <v>2200</v>
       </c>
+      <c r="AM35" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E41" s="3">
         <v>31600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>24900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>27800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>28500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>32900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>43600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>52800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>61200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>72600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>26500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>26900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>27800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>21100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>18000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>29700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>39200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>44400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>48100</v>
-      </c>
-      <c r="AI41" s="3">
-        <v>56500</v>
       </c>
       <c r="AJ41" s="3">
         <v>56500</v>
       </c>
       <c r="AK41" s="3">
+        <v>56500</v>
+      </c>
+      <c r="AL41" s="3">
         <v>36200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3997,323 +4087,332 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>1700</v>
       </c>
       <c r="I42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J42" s="3">
         <v>2100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4500</v>
-      </c>
-      <c r="P42" s="3">
-        <v>5400</v>
       </c>
       <c r="Q42" s="3">
         <v>5400</v>
       </c>
       <c r="R42" s="3">
+        <v>5400</v>
+      </c>
+      <c r="S42" s="3">
         <v>5700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2800</v>
-      </c>
-      <c r="T42" s="3">
-        <v>200</v>
       </c>
       <c r="U42" s="3">
         <v>200</v>
       </c>
       <c r="V42" s="3">
+        <v>200</v>
+      </c>
+      <c r="W42" s="3">
         <v>4500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>5200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>8700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>6100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>7500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>13100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>22100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>21900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>18800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>15200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>20000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>20500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>22500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>20500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>11400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E43" s="3">
         <v>22900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>21300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>38100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>38800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>39800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>34800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>36600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>33500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>28400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>24600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>22700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>19800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>23600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>17500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>18300</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>19600</v>
       </c>
       <c r="AC43" s="3">
         <v>19600</v>
       </c>
       <c r="AD43" s="3">
+        <v>19600</v>
+      </c>
+      <c r="AE43" s="3">
         <v>23300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>22500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>21300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>22800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>20900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>18400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>17800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>14500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E44" s="3">
         <v>80400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>85100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>86100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>85800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>85900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>86500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>86400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>87100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>91700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>89600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>88500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>77300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>68800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>65900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>60700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>58900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>54700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>51500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>48400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>49600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>48300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>49200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>49100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>50300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>53000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>58600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>58700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>57000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>51100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>45800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>40800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>39200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>40200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4344,416 +4443,428 @@
       <c r="L45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N45" s="3">
         <v>20400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>16500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>18400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>11400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>11700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>10600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E46" s="3">
         <v>149500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>158300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>167900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>167400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>163700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>170700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>160300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>165500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>177000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>183500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>181500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>177400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>160100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>160200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>159600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>164400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>163000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>164500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>108500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>110700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>111300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>113200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>108700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>111700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>118100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>128500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>132600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>137500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>133600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>140500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>136000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>143200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>138700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>107300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>101600</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>10</v>
+      <c r="D47" s="3">
+        <v>14700</v>
       </c>
       <c r="E47" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F47" s="3">
         <v>14600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>14100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>12500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>18200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>16700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>17900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>20700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>19700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>16000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4700</v>
-      </c>
-      <c r="X47" s="3">
-        <v>4000</v>
       </c>
       <c r="Y47" s="3">
         <v>4000</v>
       </c>
       <c r="Z47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA47" s="3">
         <v>10600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>10000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>16800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>16900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>13900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>12800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>13900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>11000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>20400</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>161900</v>
+      </c>
+      <c r="E48" s="3">
         <v>161400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>162200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>168900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>163900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>165800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>169100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>161700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>160100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>164200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>162800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>154500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>154900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>149500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>144700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>134000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>129700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>122500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>118500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>111000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>103800</v>
-      </c>
-      <c r="X48" s="3">
-        <v>100300</v>
       </c>
       <c r="Y48" s="3">
         <v>100300</v>
       </c>
       <c r="Z48" s="3">
+        <v>100300</v>
+      </c>
+      <c r="AA48" s="3">
         <v>92700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>88600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>86000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>82300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>74800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>65200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>58800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>46500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>42300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>27900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>27100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>27800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4761,11 +4872,11 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>1700</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -4773,11 +4884,11 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>1800</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>22600</v>
+        <v>7400</v>
       </c>
       <c r="E52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F52" s="3">
         <v>1100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7900</v>
-      </c>
-      <c r="O52" s="3">
-        <v>8100</v>
       </c>
       <c r="P52" s="3">
         <v>8100</v>
       </c>
       <c r="Q52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="R52" s="3">
         <v>7800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7500</v>
-      </c>
-      <c r="AI52" s="3">
-        <v>7800</v>
       </c>
       <c r="AJ52" s="3">
         <v>7800</v>
       </c>
       <c r="AK52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="AL52" s="3">
         <v>8100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E54" s="3">
         <v>333500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>339300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>355600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>349400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>349000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>358700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>342200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>346200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>366600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>370100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>361800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>361300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>338400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>332400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>315700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>309400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>301900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>298900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>232700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>226200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>222600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>223300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>217700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>213900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>214600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>223500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>220400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>219700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>216300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>211200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>199600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>191800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>187400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>154200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>152900</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,192 +5622,196 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E57" s="3">
         <v>11100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>18800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>16300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>17400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>15300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9500</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>8200</v>
       </c>
       <c r="AJ57" s="3">
         <v>8200</v>
       </c>
       <c r="AK57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AL57" s="3">
         <v>6700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>52500</v>
+        <v>56500</v>
       </c>
       <c r="E58" s="3">
+        <v>53100</v>
+      </c>
+      <c r="F58" s="3">
         <v>47800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>54500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>51200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>49500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>53400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>46200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>45900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>53200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>47100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>43000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>33000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>20200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>13300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>10500</v>
-      </c>
-      <c r="T58" s="3">
-        <v>10400</v>
       </c>
       <c r="U58" s="3">
         <v>10400</v>
       </c>
       <c r="V58" s="3">
+        <v>10400</v>
+      </c>
+      <c r="W58" s="3">
         <v>3400</v>
-      </c>
-      <c r="W58" s="3">
-        <v>6100</v>
       </c>
       <c r="X58" s="3">
         <v>6100</v>
       </c>
       <c r="Y58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="Z58" s="3">
         <v>5700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5600</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>10</v>
@@ -5685,11 +5819,11 @@
       <c r="AC58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE58" s="3">
         <v>300</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>10</v>
@@ -5703,8 +5837,8 @@
       <c r="AI58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
+      <c r="AJ58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AK58" s="3">
         <v>0</v>
@@ -5712,261 +5846,270 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>10</v>
+      <c r="D59" s="3">
+        <v>6000</v>
       </c>
       <c r="E59" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F59" s="3">
         <v>7100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>9200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E60" s="3">
         <v>75300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>74200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>78800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>74600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>72000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>81600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>67700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>67300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>72800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>75300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>72900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>70900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>46800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>47800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>37300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>39100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>28100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>26000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>27500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>23200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>16900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>28700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>25400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>25900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>21200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>22600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>17600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>16100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>16000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1900</v>
+        <v>6700</v>
       </c>
       <c r="E61" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F61" s="3">
         <v>7800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2200</v>
-      </c>
-      <c r="I61" s="3">
-        <v>2400</v>
       </c>
       <c r="J61" s="3">
         <v>2400</v>
       </c>
       <c r="K61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L61" s="3">
         <v>1200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5980,11 +6123,11 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -6042,88 +6185,91 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10200</v>
+        <v>2100</v>
       </c>
       <c r="E62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F62" s="3">
         <v>2500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3700</v>
-      </c>
-      <c r="S62" s="3">
-        <v>3800</v>
       </c>
       <c r="T62" s="3">
         <v>3800</v>
       </c>
       <c r="U62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="V62" s="3">
         <v>4300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4500</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>3100</v>
       </c>
       <c r="Z62" s="3">
         <v>3100</v>
       </c>
       <c r="AA62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AB62" s="3">
         <v>1300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>300</v>
       </c>
       <c r="AD62" s="3">
         <v>300</v>
@@ -6138,22 +6284,25 @@
         <v>300</v>
       </c>
       <c r="AH62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI62" s="3">
         <v>400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E66" s="3">
         <v>87300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>84400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>89400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>86300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>83900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>89600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>74100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>71800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>78300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>148500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>144600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>144900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>122700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>120900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>109900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>109600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>106800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>106200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>37300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>37900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>35600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>35500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>30800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>32700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>29300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>30000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>26600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>27400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>23200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>21800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>20500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>21200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>3500</v>
       </c>
+      <c r="AM70" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-52500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-43700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-38600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-35600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-34100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-32000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-28400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-22600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-17500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-14200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-15500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-21300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-26800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-30000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-32900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-36700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-41100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-44500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-46600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-47600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-48000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-47800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-45700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-44800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-46300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-45200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-44100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-48100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-52000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-54800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-58000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-62400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-64300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>176200</v>
+      </c>
+      <c r="E76" s="3">
         <v>181500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>189200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>197200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>196100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>197600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>200500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>200700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>206300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>216500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>218100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>213600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>212800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>212200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>208000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>202200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>196300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>191600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>189100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>191900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>184800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>183500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>184400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>183400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>187800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>188000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>187300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>187600</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>186100</v>
       </c>
       <c r="AF76" s="3">
         <v>186100</v>
       </c>
       <c r="AG76" s="3">
+        <v>186100</v>
+      </c>
+      <c r="AH76" s="3">
         <v>180300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>172900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>166500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>163400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>129500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1400</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-1100</v>
       </c>
       <c r="AC81" s="3">
         <v>-1100</v>
       </c>
       <c r="AD81" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AE81" s="3">
         <v>3900</v>
       </c>
       <c r="AF81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AG81" s="3">
         <v>2800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>600</v>
-      </c>
-      <c r="AK81" s="3">
-        <v>2200</v>
       </c>
       <c r="AL81" s="3">
         <v>2200</v>
       </c>
+      <c r="AM81" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8006,13 +8205,13 @@
         <v>2200</v>
       </c>
       <c r="E83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F83" s="3">
         <v>2300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2100</v>
       </c>
       <c r="H83" s="3">
         <v>2100</v>
@@ -8024,19 +8223,19 @@
         <v>2100</v>
       </c>
       <c r="K83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="L83" s="3">
         <v>2000</v>
       </c>
       <c r="M83" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="N83" s="3">
         <v>2100</v>
       </c>
       <c r="O83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="P83" s="3">
         <v>2000</v>
@@ -8045,19 +8244,19 @@
         <v>2000</v>
       </c>
       <c r="R83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S83" s="3">
         <v>1800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1400</v>
-      </c>
-      <c r="V83" s="3">
-        <v>1000</v>
       </c>
       <c r="W83" s="3">
         <v>1000</v>
@@ -8066,25 +8265,25 @@
         <v>1000</v>
       </c>
       <c r="Y83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>1100</v>
       </c>
       <c r="AF83" s="3">
         <v>1100</v>
@@ -8102,13 +8301,16 @@
         <v>1100</v>
       </c>
       <c r="AK83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AL83" s="3">
         <v>1200</v>
       </c>
+      <c r="AM83" s="3">
+        <v>1200</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>10</v>
+      <c r="D89" s="3">
+        <v>-4600</v>
       </c>
       <c r="E89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F89" s="3">
         <v>1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>7000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>10</v>
+      <c r="D91" s="3">
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-10100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-14700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AK91" s="3">
-        <v>-500</v>
       </c>
       <c r="AL91" s="3">
         <v>-500</v>
       </c>
+      <c r="AM91" s="3">
+        <v>-500</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>10</v>
+      <c r="D94" s="3">
+        <v>-800</v>
       </c>
       <c r="E94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>6900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>10</v>
+      <c r="D100" s="3">
+        <v>-300</v>
       </c>
       <c r="E100" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-5000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>14100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>53600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1800</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>5800</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>400</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>100</v>
       </c>
       <c r="AD100" s="3">
         <v>100</v>
       </c>
       <c r="AE100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>32200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1900</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>200</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ101" s="3">
         <v>100</v>
       </c>
       <c r="AK101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-3100</v>
       </c>
       <c r="E102" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-5000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>50200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6800</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>-900</v>
       </c>
       <c r="Z102" s="3">
         <v>-900</v>
       </c>
       <c r="AA102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AB102" s="3">
         <v>7700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-9500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AI102" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>20400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>6500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>3500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXTI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>AXTI</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E8" s="3">
         <v>28000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>27900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>26800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>35200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>39500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>39700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>37700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>27000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>25500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>20700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>19800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>24800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>20200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>22200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>28600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>27100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>24400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>26300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>28200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>23600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>20600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>20300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E9" s="3">
         <v>21700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>24100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>25600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>23100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>15400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>15200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>14500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>16400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>18000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>16100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>16500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>17000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>16300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>14300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>12700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E10" s="3">
         <v>6200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>12200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>6700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>5800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>10600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>11000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>9600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>11200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>7300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>6300</v>
-      </c>
-      <c r="AM10" s="3">
-        <v>7600</v>
       </c>
       <c r="AN10" s="3">
         <v>7600</v>
       </c>
+      <c r="AO10" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,124 +1220,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>1300</v>
       </c>
       <c r="AE12" s="3">
         <v>1300</v>
       </c>
       <c r="AF12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AG12" s="3">
         <v>1700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1400</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1440,8 +1456,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1478,8 +1497,8 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1541,23 +1560,26 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1568,34 +1590,34 @@
         <v>2300</v>
       </c>
       <c r="F15" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="G15" s="3">
         <v>2200</v>
       </c>
       <c r="H15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I15" s="3">
         <v>2300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2200</v>
       </c>
       <c r="J15" s="3">
         <v>2200</v>
       </c>
       <c r="K15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L15" s="3">
         <v>2300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2200</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2100</v>
       </c>
       <c r="N15" s="3">
         <v>2100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1672,8 +1694,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E17" s="3">
         <v>29100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>30600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>34200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>36000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>34700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>32200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>29800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>27800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>23300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>20300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>19600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>22900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>24300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>22600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>20500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>22600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>22900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>21300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>19200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>18000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>5300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,240 +2017,247 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AM20" s="3">
-        <v>-300</v>
       </c>
       <c r="AN20" s="3">
         <v>-300</v>
       </c>
+      <c r="AO20" s="3">
+        <v>-300</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
         <v>1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>5900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2226,25 +2265,25 @@
         <v>400</v>
       </c>
       <c r="E22" s="3">
+        <v>400</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>300</v>
       </c>
       <c r="G22" s="3">
         <v>300</v>
       </c>
       <c r="H22" s="3">
+        <v>300</v>
+      </c>
+      <c r="I22" s="3">
         <v>400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>300</v>
       </c>
       <c r="J22" s="3">
         <v>300</v>
       </c>
       <c r="K22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
@@ -2256,7 +2295,7 @@
         <v>400</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2333,124 +2372,130 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>4700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2458,115 +2503,118 @@
         <v>500</v>
       </c>
       <c r="E24" s="3">
+        <v>500</v>
+      </c>
+      <c r="F24" s="3">
         <v>600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>300</v>
       </c>
       <c r="K24" s="3">
         <v>300</v>
       </c>
       <c r="L24" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="M24" s="3">
         <v>-100</v>
       </c>
       <c r="N24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>400</v>
       </c>
       <c r="AG24" s="3">
         <v>400</v>
       </c>
       <c r="AH24" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI24" s="3">
         <v>300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>200</v>
       </c>
-      <c r="AM24" s="3">
-        <v>0</v>
-      </c>
       <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-1100</v>
       </c>
       <c r="AE27" s="3">
         <v>-1100</v>
       </c>
       <c r="AF27" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AG27" s="3">
         <v>3900</v>
       </c>
       <c r="AH27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AI27" s="3">
         <v>2800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>600</v>
-      </c>
-      <c r="AM27" s="3">
-        <v>2200</v>
       </c>
       <c r="AN27" s="3">
         <v>2200</v>
       </c>
+      <c r="AO27" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3443,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>1500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>800</v>
-      </c>
-      <c r="AM32" s="3">
-        <v>300</v>
       </c>
       <c r="AN32" s="3">
         <v>300</v>
       </c>
+      <c r="AO32" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>-1100</v>
       </c>
       <c r="AE33" s="3">
         <v>-1100</v>
       </c>
       <c r="AF33" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AG33" s="3">
         <v>3900</v>
       </c>
       <c r="AH33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AI33" s="3">
         <v>2800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>600</v>
-      </c>
-      <c r="AM33" s="3">
-        <v>2200</v>
       </c>
       <c r="AN33" s="3">
         <v>2200</v>
       </c>
+      <c r="AO33" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>-1100</v>
       </c>
       <c r="AE35" s="3">
         <v>-1100</v>
       </c>
       <c r="AF35" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AG35" s="3">
         <v>3900</v>
       </c>
       <c r="AH35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AI35" s="3">
         <v>2800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>600</v>
-      </c>
-      <c r="AM35" s="3">
-        <v>2200</v>
       </c>
       <c r="AN35" s="3">
         <v>2200</v>
       </c>
+      <c r="AO35" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4131,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>120300</v>
+      </c>
+      <c r="E41" s="3">
         <v>23100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>27000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>31600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>24900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>37800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>35400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>32900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>41000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>29500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>43600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>52800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>61200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>72600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>22400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>26500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>20100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>26900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>27800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>28700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>21100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>16500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>18000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>29700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>39200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>44400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>48100</v>
-      </c>
-      <c r="AK41" s="3">
-        <v>56500</v>
       </c>
       <c r="AL41" s="3">
         <v>56500</v>
       </c>
       <c r="AM41" s="3">
+        <v>56500</v>
+      </c>
+      <c r="AN41" s="3">
         <v>36200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>29700</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4183,335 +4272,344 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>1700</v>
       </c>
       <c r="K42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L42" s="3">
         <v>2100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>7200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4500</v>
-      </c>
-      <c r="R42" s="3">
-        <v>5400</v>
       </c>
       <c r="S42" s="3">
         <v>5400</v>
       </c>
       <c r="T42" s="3">
+        <v>5400</v>
+      </c>
+      <c r="U42" s="3">
         <v>5700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2800</v>
-      </c>
-      <c r="V42" s="3">
-        <v>200</v>
       </c>
       <c r="W42" s="3">
         <v>200</v>
       </c>
       <c r="X42" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y42" s="3">
         <v>4500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>8700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>6100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>7500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>13100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>22100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>21900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>18800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>15200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>20500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>22500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>20500</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>11400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E43" s="3">
         <v>33800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>22800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>27200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>19900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>21300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>38100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>38800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>39800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>34800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>36600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>33500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>28400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>24600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>22700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>19800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>23600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>19000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>17500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>18300</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>19600</v>
       </c>
       <c r="AE43" s="3">
         <v>19600</v>
       </c>
       <c r="AF43" s="3">
+        <v>19600</v>
+      </c>
+      <c r="AG43" s="3">
         <v>23300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>22500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>21300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>22800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>20900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>18400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>17800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>14500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>81700</v>
+      </c>
+      <c r="E44" s="3">
         <v>77700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>80100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>80400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>85100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>86100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>85800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>85900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>86500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>86400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>87100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>91700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>89600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>88500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>77300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>68800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>65900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>60700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>58900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>54700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>51500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>48400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>49600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>48300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>49200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>49100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>50300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>53000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>58600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>58700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>57000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>51100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>45800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>40800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>40600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>39200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>40200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4548,439 +4646,451 @@
       <c r="N45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="3">
         <v>20400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>16500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>18400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>11400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>11700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>10600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>9400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>6700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>5100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>246600</v>
+      </c>
+      <c r="E46" s="3">
         <v>149800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>145000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>149500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>158300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>167900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>167400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>163700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>170700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>160300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>165500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>177000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>183500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>181500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>177400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>160100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>160200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>159600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>164400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>163000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>164500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>108500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>110700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>111300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>113200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>108700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>111700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>118100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>128500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>132600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>137500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>133600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>140500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>136000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>143200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>138700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>107300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>101600</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E47" s="3">
         <v>15300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>14000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>18200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>16700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>17900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>20900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>20700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>19700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>16000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4700</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>4000</v>
       </c>
       <c r="AA47" s="3">
         <v>4000</v>
       </c>
       <c r="AB47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AC47" s="3">
         <v>10600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>10000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>16800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>16900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>13900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>12800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>13900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>11000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>20400</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>163800</v>
+      </c>
+      <c r="E48" s="3">
         <v>161400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>161900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>161400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>162200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>168900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>163900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>165800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>169100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>161700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>160100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>164200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>162800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>154500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>154900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>149500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>144700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>134000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>129700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>122500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>118500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>111000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>103800</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>100300</v>
       </c>
       <c r="AA48" s="3">
         <v>100300</v>
       </c>
       <c r="AB48" s="3">
+        <v>100300</v>
+      </c>
+      <c r="AC48" s="3">
         <v>92700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>88600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>86000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>82300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>74800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>65200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>58800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>42300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>27900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>27100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>27800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4989,11 +5099,11 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>1700</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -5001,11 +5111,11 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>1800</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
@@ -5090,8 +5200,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5438,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E52" s="3">
         <v>7600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>7400</v>
       </c>
       <c r="F52" s="3">
         <v>7400</v>
       </c>
       <c r="G52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H52" s="3">
         <v>1100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7900</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>8100</v>
       </c>
       <c r="R52" s="3">
         <v>8100</v>
       </c>
       <c r="S52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="T52" s="3">
         <v>7800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>7500</v>
-      </c>
-      <c r="AK52" s="3">
-        <v>7800</v>
       </c>
       <c r="AL52" s="3">
         <v>7800</v>
       </c>
       <c r="AM52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="AN52" s="3">
         <v>8100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>433800</v>
+      </c>
+      <c r="E54" s="3">
         <v>334000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>329000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>333500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>339300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>355600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>349400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>349000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>358700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>342200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>346200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>366600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>370100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>361800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>361300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>338400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>332400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>315700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>309400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>301900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>298900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>232700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>226200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>222600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>223300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>217700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>213900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>214600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>223500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>220400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>219700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>216300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>211200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>199600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>191800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>187400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>154200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>152900</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,204 +5883,208 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E57" s="3">
         <v>10800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>16300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>17400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>15300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9500</v>
-      </c>
-      <c r="AK57" s="3">
-        <v>8200</v>
       </c>
       <c r="AL57" s="3">
         <v>8200</v>
       </c>
       <c r="AM57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AN57" s="3">
         <v>6700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E58" s="3">
         <v>62100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>56500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>53100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>47800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>54500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>51200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>49500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>53400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>46200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>45900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>53200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>47100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>43000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>33000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>20200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>13300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>10500</v>
-      </c>
-      <c r="V58" s="3">
-        <v>10400</v>
       </c>
       <c r="W58" s="3">
         <v>10400</v>
       </c>
       <c r="X58" s="3">
+        <v>10400</v>
+      </c>
+      <c r="Y58" s="3">
         <v>3400</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>6100</v>
       </c>
       <c r="Z58" s="3">
         <v>6100</v>
       </c>
       <c r="AA58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AB58" s="3">
         <v>5700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>5600</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>10</v>
@@ -5959,11 +6092,11 @@
       <c r="AE58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG58" s="3">
         <v>300</v>
-      </c>
-      <c r="AG58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>10</v>
@@ -5977,8 +6110,8 @@
       <c r="AK58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AL58" s="3">
-        <v>0</v>
+      <c r="AL58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AM58" s="3">
         <v>0</v>
@@ -5986,240 +6119,249 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>9300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>7900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>9300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>90500</v>
+      </c>
+      <c r="E60" s="3">
         <v>84900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>79500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>75300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>74200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>78800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>74600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>72000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>81600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>67700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>67300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>72800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>75300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>72900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>70900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>46800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>47800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>37300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>39500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>39100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>26500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>28100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>26000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>27500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>23200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>17400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>28700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>25400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>25900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>21200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>22600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>18800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>17600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>16100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>16000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6227,38 +6369,38 @@
         <v>6600</v>
       </c>
       <c r="E61" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F61" s="3">
         <v>6700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9800</v>
       </c>
-      <c r="G61" s="3">
-        <v>7800</v>
-      </c>
       <c r="H61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I61" s="3">
         <v>8400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2200</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2400</v>
       </c>
       <c r="L61" s="3">
         <v>2400</v>
       </c>
       <c r="M61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N61" s="3">
         <v>1200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -6272,11 +6414,11 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>900</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -6334,94 +6476,97 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="E62" s="3">
         <v>2100</v>
       </c>
       <c r="F62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G62" s="3">
         <v>2300</v>
       </c>
-      <c r="G62" s="3">
-        <v>2500</v>
-      </c>
       <c r="H62" s="3">
+        <v>8300</v>
+      </c>
+      <c r="I62" s="3">
         <v>2200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3700</v>
-      </c>
-      <c r="U62" s="3">
-        <v>3800</v>
       </c>
       <c r="V62" s="3">
         <v>3800</v>
       </c>
       <c r="W62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="X62" s="3">
         <v>4300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4500</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>3100</v>
       </c>
       <c r="AB62" s="3">
         <v>3100</v>
       </c>
       <c r="AC62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD62" s="3">
         <v>1300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>300</v>
       </c>
       <c r="AF62" s="3">
         <v>300</v>
@@ -6436,22 +6581,25 @@
         <v>300</v>
       </c>
       <c r="AJ62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK62" s="3">
         <v>400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>99100</v>
+      </c>
+      <c r="E66" s="3">
         <v>93600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>88400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>87300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>84400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>89400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>86300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>83900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>89600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>74100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>71800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>78300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>148500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>144600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>144900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>122700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>120900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>109900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>109600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>106800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>106200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>37300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>37900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>35600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>35500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>30800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>22600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>32700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>29300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>30000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>26600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>27400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>23200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>21800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>20500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>21200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>3500</v>
       </c>
+      <c r="AO70" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-61400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-59500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-52500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-43700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-38600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-35600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-34100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-32000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-28400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-22600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-14200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-15500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-21300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-26800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-30000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-32900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-36700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-41100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-44500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-46600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-47600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-48000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-47800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-45700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-44800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-46300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-45200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-44100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-48100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-52000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-54800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-58000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-62400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-64300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-65000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>269800</v>
+      </c>
+      <c r="E76" s="3">
         <v>175600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>176200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>181500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>189200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>197200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>196100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>197600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>200500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>200700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>206300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>216500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>218100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>213600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>212800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>212200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>208000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>202200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>196300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>191600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>189100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>191900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>184800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>183500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>184400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>183400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>187800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>188000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>187300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>187600</v>
-      </c>
-      <c r="AG76" s="3">
-        <v>186100</v>
       </c>
       <c r="AH76" s="3">
         <v>186100</v>
       </c>
       <c r="AI76" s="3">
+        <v>186100</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>180300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>172900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>166500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>163400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>129500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>-1100</v>
       </c>
       <c r="AE81" s="3">
         <v>-1100</v>
       </c>
       <c r="AF81" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="AG81" s="3">
         <v>3900</v>
       </c>
       <c r="AH81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AI81" s="3">
         <v>2800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>600</v>
-      </c>
-      <c r="AM81" s="3">
-        <v>2200</v>
       </c>
       <c r="AN81" s="3">
         <v>2200</v>
       </c>
+      <c r="AO81" s="3">
+        <v>2200</v>
+      </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,28 +8592,29 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E83" s="3">
         <v>2300</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2200</v>
       </c>
       <c r="F83" s="3">
         <v>2200</v>
       </c>
       <c r="G83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H83" s="3">
         <v>2300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2100</v>
       </c>
       <c r="J83" s="3">
         <v>2100</v>
@@ -8428,19 +8626,19 @@
         <v>2100</v>
       </c>
       <c r="M83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="N83" s="3">
         <v>2000</v>
       </c>
       <c r="O83" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="P83" s="3">
         <v>2100</v>
       </c>
       <c r="Q83" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="R83" s="3">
         <v>2000</v>
@@ -8449,19 +8647,19 @@
         <v>2000</v>
       </c>
       <c r="T83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U83" s="3">
         <v>1800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>1000</v>
       </c>
       <c r="Y83" s="3">
         <v>1000</v>
@@ -8470,25 +8668,25 @@
         <v>1000</v>
       </c>
       <c r="AA83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1200</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>1100</v>
       </c>
       <c r="AH83" s="3">
         <v>1100</v>
@@ -8506,13 +8704,16 @@
         <v>1100</v>
       </c>
       <c r="AM83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AN83" s="3">
         <v>1200</v>
       </c>
+      <c r="AO83" s="3">
+        <v>1200</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>7000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-14600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-10100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-14700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AM91" s="3">
-        <v>-500</v>
       </c>
       <c r="AN91" s="3">
         <v>-500</v>
       </c>
+      <c r="AO91" s="3">
+        <v>-500</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2200</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-800</v>
       </c>
       <c r="F94" s="3">
         <v>-800</v>
       </c>
       <c r="G94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>6900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-11600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-13900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9987,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,8 +10026,8 @@
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9871,8 +10104,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10461,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E100" s="3">
         <v>5200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>13200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>14100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>7900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>53600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5800</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>400</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>100</v>
       </c>
       <c r="AF100" s="3">
         <v>100</v>
       </c>
       <c r="AG100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>32200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>200</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL101" s="3">
         <v>100</v>
       </c>
       <c r="AM101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN101" s="3">
         <v>-900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>97200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>50200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6800</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>-900</v>
       </c>
       <c r="AB102" s="3">
         <v>-900</v>
       </c>
       <c r="AC102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AD102" s="3">
         <v>7700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-9500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AK102" s="3">
-        <v>0</v>
-      </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>20400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>6500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>3500</v>
       </c>
     </row>
